--- a/reports/Security Findings.xlsx
+++ b/reports/Security Findings.xlsx
@@ -414,7 +414,7 @@
         <v>Generated At</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-29T14:22:29.074Z</v>
+        <v>2026-07-31T11:19:36.539Z</v>
       </c>
     </row>
     <row r="3">
@@ -422,7 +422,7 @@
         <v>Total Findings</v>
       </c>
       <c r="B3">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
@@ -430,7 +430,7 @@
         <v>Pass</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
@@ -438,7 +438,7 @@
         <v>Fail</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -446,7 +446,7 @@
         <v>Not Applicable</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -532,7 +532,7 @@
         <v>Automated assessment item for authorization coverage.</v>
       </c>
       <c r="E3" t="str">
-        <v>Potential issue found in Authorization workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F3" t="str">
         <v>src/pages/LandingPage.tsx</v>
@@ -541,10 +541,10 @@
         <v>/</v>
       </c>
       <c r="H3" t="str">
-        <v>Review the Authorization design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I3" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="4">
@@ -573,7 +573,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I4" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I5" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="6">
@@ -619,7 +619,7 @@
         <v>Automated assessment item for session coverage.</v>
       </c>
       <c r="E6" t="str">
-        <v>Potential issue found in Session workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F6" t="str">
         <v>src/pages/EmergencyContacts.tsx</v>
@@ -628,10 +628,10 @@
         <v>/contacts</v>
       </c>
       <c r="H6" t="str">
-        <v>Review the Session design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I6" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="7">
@@ -706,7 +706,7 @@
         <v>Automated assessment item for nosql injection coverage.</v>
       </c>
       <c r="E9" t="str">
-        <v>Potential issue found in NoSQL Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F9" t="str">
         <v>src/pages/Login.tsx</v>
@@ -715,10 +715,10 @@
         <v>/login</v>
       </c>
       <c r="H9" t="str">
-        <v>Review the NoSQL Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I9" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="10">
@@ -747,7 +747,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I10" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="11">
@@ -776,7 +776,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I11" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="12">
@@ -787,13 +787,13 @@
         <v>SSRF</v>
       </c>
       <c r="C12" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D12" t="str">
         <v>Automated assessment item for ssrf coverage.</v>
       </c>
       <c r="E12" t="str">
-        <v>Potential issue found in SSRF workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F12" t="str">
         <v>src/pages/SendSOS.tsx</v>
@@ -802,10 +802,10 @@
         <v>/send-sos</v>
       </c>
       <c r="H12" t="str">
-        <v>Review the SSRF design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I12" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="13">
@@ -880,7 +880,7 @@
         <v>Automated assessment item for path traversal coverage.</v>
       </c>
       <c r="E15" t="str">
-        <v>Potential issue found in Path Traversal workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F15" t="str">
         <v>src/pages/VolunteerDashboard.tsx</v>
@@ -889,10 +889,10 @@
         <v>/volunteer</v>
       </c>
       <c r="H15" t="str">
-        <v>Review the Path Traversal design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I15" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="16">
@@ -921,7 +921,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I16" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="17">
@@ -950,7 +950,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I17" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="18">
@@ -967,7 +967,7 @@
         <v>Automated assessment item for api keys coverage.</v>
       </c>
       <c r="E18" t="str">
-        <v>Potential issue found in API Keys workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F18" t="str">
         <v>src/pages/AdminDashboard.tsx</v>
@@ -976,10 +976,10 @@
         <v>/admin</v>
       </c>
       <c r="H18" t="str">
-        <v>Review the API Keys design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I18" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="19">
@@ -1054,7 +1054,7 @@
         <v>Automated assessment item for security headers coverage.</v>
       </c>
       <c r="E21" t="str">
-        <v>Potential issue found in Security Headers workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F21" t="str">
         <v>src/pages/Dashboard.tsx</v>
@@ -1063,10 +1063,10 @@
         <v>/dashboard</v>
       </c>
       <c r="H21" t="str">
-        <v>Review the Security Headers design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I21" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="22">
@@ -1095,7 +1095,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I22" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="23">
@@ -1124,7 +1124,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I23" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="24">
@@ -1141,7 +1141,7 @@
         <v>Automated assessment item for cookies coverage.</v>
       </c>
       <c r="E24" t="str">
-        <v>Potential issue found in Cookies workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F24" t="str">
         <v>src/pages/UserProfile.tsx</v>
@@ -1150,10 +1150,10 @@
         <v>/profile</v>
       </c>
       <c r="H24" t="str">
-        <v>Review the Cookies design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I24" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="25">
@@ -1222,13 +1222,13 @@
         <v>Configuration</v>
       </c>
       <c r="C27" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D27" t="str">
         <v>Automated assessment item for configuration coverage.</v>
       </c>
       <c r="E27" t="str">
-        <v>Potential issue found in Configuration workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F27" t="str">
         <v>src/pages/Settings.tsx</v>
@@ -1237,10 +1237,10 @@
         <v>/settings</v>
       </c>
       <c r="H27" t="str">
-        <v>Review the Configuration design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I27" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="28">
@@ -1269,7 +1269,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I28" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="29">
@@ -1298,7 +1298,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I29" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="30">
@@ -1315,7 +1315,7 @@
         <v>Automated assessment item for input validation coverage.</v>
       </c>
       <c r="E30" t="str">
-        <v>Potential issue found in Input Validation workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F30" t="str">
         <v>src/App.tsx</v>
@@ -1324,10 +1324,10 @@
         <v>*</v>
       </c>
       <c r="H30" t="str">
-        <v>Review the Input Validation design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I30" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="31">
@@ -1402,7 +1402,7 @@
         <v>Automated assessment item for authentication coverage.</v>
       </c>
       <c r="E33" t="str">
-        <v>Potential issue found in Authentication workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F33" t="str">
         <v>src/pages/EmergencyChat.tsx</v>
@@ -1411,10 +1411,10 @@
         <v>/chat</v>
       </c>
       <c r="H33" t="str">
-        <v>Review the Authentication design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I33" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="34">
@@ -1443,7 +1443,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I34" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="35">
@@ -1472,7 +1472,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I35" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="36">
@@ -1489,7 +1489,7 @@
         <v>Automated assessment item for jwt coverage.</v>
       </c>
       <c r="E36" t="str">
-        <v>Potential issue found in JWT workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F36" t="str">
         <v>src/pages/EmergencyHistory.tsx</v>
@@ -1498,10 +1498,10 @@
         <v>/history</v>
       </c>
       <c r="H36" t="str">
-        <v>Review the JWT design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I36" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="37">
@@ -1576,7 +1576,7 @@
         <v>Automated assessment item for sql injection coverage.</v>
       </c>
       <c r="E39" t="str">
-        <v>Potential issue found in SQL Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F39" t="str">
         <v>src/pages/Registration.tsx</v>
@@ -1585,10 +1585,10 @@
         <v>/register</v>
       </c>
       <c r="H39" t="str">
-        <v>Review the SQL Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I39" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="40">
@@ -1617,7 +1617,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I40" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="41">
@@ -1646,7 +1646,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I41" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="42">
@@ -1657,13 +1657,13 @@
         <v>CSRF</v>
       </c>
       <c r="C42" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D42" t="str">
         <v>Automated assessment item for csrf coverage.</v>
       </c>
       <c r="E42" t="str">
-        <v>Potential issue found in CSRF workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F42" t="str">
         <v>src/pages/LiveTracking.tsx</v>
@@ -1672,10 +1672,10 @@
         <v>/tracking</v>
       </c>
       <c r="H42" t="str">
-        <v>Review the CSRF design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I42" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="43">
@@ -1750,7 +1750,7 @@
         <v>Automated assessment item for command injection coverage.</v>
       </c>
       <c r="E45" t="str">
-        <v>Potential issue found in Command Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F45" t="str">
         <v>src/pages/LandingPage.tsx</v>
@@ -1759,10 +1759,10 @@
         <v>/</v>
       </c>
       <c r="H45" t="str">
-        <v>Review the Command Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I45" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="46">
@@ -1791,7 +1791,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I46" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="47">
@@ -1820,7 +1820,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I47" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="48">
@@ -1837,7 +1837,7 @@
         <v>Automated assessment item for secrets coverage.</v>
       </c>
       <c r="E48" t="str">
-        <v>Potential issue found in Secrets workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F48" t="str">
         <v>src/pages/EmergencyContacts.tsx</v>
@@ -1846,10 +1846,10 @@
         <v>/contacts</v>
       </c>
       <c r="H48" t="str">
-        <v>Review the Secrets design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I48" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="49">
@@ -1924,7 +1924,7 @@
         <v>Automated assessment item for sensitive data coverage.</v>
       </c>
       <c r="E51" t="str">
-        <v>Potential issue found in Sensitive Data workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F51" t="str">
         <v>src/pages/Login.tsx</v>
@@ -1933,10 +1933,10 @@
         <v>/login</v>
       </c>
       <c r="H51" t="str">
-        <v>Review the Sensitive Data design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I51" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
   </sheetData>
@@ -1948,7 +1948,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I301"/>
+  <dimension ref="A1:I401"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2022,7 +2022,7 @@
         <v>Automated assessment item for authorization coverage.</v>
       </c>
       <c r="E3" t="str">
-        <v>Potential issue found in Authorization workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F3" t="str">
         <v>src/pages/LandingPage.tsx</v>
@@ -2031,10 +2031,10 @@
         <v>/</v>
       </c>
       <c r="H3" t="str">
-        <v>Review the Authorization design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I3" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="4">
@@ -2063,7 +2063,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I4" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="5">
@@ -2092,7 +2092,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I5" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="6">
@@ -2109,7 +2109,7 @@
         <v>Automated assessment item for session coverage.</v>
       </c>
       <c r="E6" t="str">
-        <v>Potential issue found in Session workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F6" t="str">
         <v>src/pages/EmergencyContacts.tsx</v>
@@ -2118,10 +2118,10 @@
         <v>/contacts</v>
       </c>
       <c r="H6" t="str">
-        <v>Review the Session design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I6" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="7">
@@ -2196,7 +2196,7 @@
         <v>Automated assessment item for nosql injection coverage.</v>
       </c>
       <c r="E9" t="str">
-        <v>Potential issue found in NoSQL Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F9" t="str">
         <v>src/pages/Login.tsx</v>
@@ -2205,10 +2205,10 @@
         <v>/login</v>
       </c>
       <c r="H9" t="str">
-        <v>Review the NoSQL Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I9" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="10">
@@ -2237,7 +2237,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I10" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="11">
@@ -2266,7 +2266,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I11" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="12">
@@ -2277,13 +2277,13 @@
         <v>SSRF</v>
       </c>
       <c r="C12" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D12" t="str">
         <v>Automated assessment item for ssrf coverage.</v>
       </c>
       <c r="E12" t="str">
-        <v>Potential issue found in SSRF workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F12" t="str">
         <v>src/pages/SendSOS.tsx</v>
@@ -2292,10 +2292,10 @@
         <v>/send-sos</v>
       </c>
       <c r="H12" t="str">
-        <v>Review the SSRF design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I12" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="13">
@@ -2370,7 +2370,7 @@
         <v>Automated assessment item for path traversal coverage.</v>
       </c>
       <c r="E15" t="str">
-        <v>Potential issue found in Path Traversal workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F15" t="str">
         <v>src/pages/VolunteerDashboard.tsx</v>
@@ -2379,10 +2379,10 @@
         <v>/volunteer</v>
       </c>
       <c r="H15" t="str">
-        <v>Review the Path Traversal design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I15" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="16">
@@ -2411,7 +2411,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I16" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="17">
@@ -2440,7 +2440,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I17" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="18">
@@ -2457,7 +2457,7 @@
         <v>Automated assessment item for api keys coverage.</v>
       </c>
       <c r="E18" t="str">
-        <v>Potential issue found in API Keys workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F18" t="str">
         <v>src/pages/AdminDashboard.tsx</v>
@@ -2466,10 +2466,10 @@
         <v>/admin</v>
       </c>
       <c r="H18" t="str">
-        <v>Review the API Keys design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I18" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="19">
@@ -2544,7 +2544,7 @@
         <v>Automated assessment item for security headers coverage.</v>
       </c>
       <c r="E21" t="str">
-        <v>Potential issue found in Security Headers workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F21" t="str">
         <v>src/pages/Dashboard.tsx</v>
@@ -2553,10 +2553,10 @@
         <v>/dashboard</v>
       </c>
       <c r="H21" t="str">
-        <v>Review the Security Headers design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I21" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="22">
@@ -2585,7 +2585,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I22" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="23">
@@ -2614,7 +2614,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I23" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="24">
@@ -2631,7 +2631,7 @@
         <v>Automated assessment item for cookies coverage.</v>
       </c>
       <c r="E24" t="str">
-        <v>Potential issue found in Cookies workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F24" t="str">
         <v>src/pages/UserProfile.tsx</v>
@@ -2640,10 +2640,10 @@
         <v>/profile</v>
       </c>
       <c r="H24" t="str">
-        <v>Review the Cookies design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I24" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="25">
@@ -2712,13 +2712,13 @@
         <v>Configuration</v>
       </c>
       <c r="C27" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D27" t="str">
         <v>Automated assessment item for configuration coverage.</v>
       </c>
       <c r="E27" t="str">
-        <v>Potential issue found in Configuration workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F27" t="str">
         <v>src/pages/Settings.tsx</v>
@@ -2727,10 +2727,10 @@
         <v>/settings</v>
       </c>
       <c r="H27" t="str">
-        <v>Review the Configuration design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I27" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="28">
@@ -2759,7 +2759,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I28" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="29">
@@ -2788,7 +2788,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I29" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="30">
@@ -2805,7 +2805,7 @@
         <v>Automated assessment item for input validation coverage.</v>
       </c>
       <c r="E30" t="str">
-        <v>Potential issue found in Input Validation workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F30" t="str">
         <v>src/App.tsx</v>
@@ -2814,10 +2814,10 @@
         <v>*</v>
       </c>
       <c r="H30" t="str">
-        <v>Review the Input Validation design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I30" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="31">
@@ -2892,7 +2892,7 @@
         <v>Automated assessment item for authentication coverage.</v>
       </c>
       <c r="E33" t="str">
-        <v>Potential issue found in Authentication workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F33" t="str">
         <v>src/pages/EmergencyChat.tsx</v>
@@ -2901,10 +2901,10 @@
         <v>/chat</v>
       </c>
       <c r="H33" t="str">
-        <v>Review the Authentication design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I33" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="34">
@@ -2933,7 +2933,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I34" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="35">
@@ -2962,7 +2962,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I35" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="36">
@@ -2979,7 +2979,7 @@
         <v>Automated assessment item for jwt coverage.</v>
       </c>
       <c r="E36" t="str">
-        <v>Potential issue found in JWT workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F36" t="str">
         <v>src/pages/EmergencyHistory.tsx</v>
@@ -2988,10 +2988,10 @@
         <v>/history</v>
       </c>
       <c r="H36" t="str">
-        <v>Review the JWT design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I36" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="37">
@@ -3066,7 +3066,7 @@
         <v>Automated assessment item for sql injection coverage.</v>
       </c>
       <c r="E39" t="str">
-        <v>Potential issue found in SQL Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F39" t="str">
         <v>src/pages/Registration.tsx</v>
@@ -3075,10 +3075,10 @@
         <v>/register</v>
       </c>
       <c r="H39" t="str">
-        <v>Review the SQL Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I39" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="40">
@@ -3107,7 +3107,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I40" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="41">
@@ -3136,7 +3136,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I41" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="42">
@@ -3147,13 +3147,13 @@
         <v>CSRF</v>
       </c>
       <c r="C42" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D42" t="str">
         <v>Automated assessment item for csrf coverage.</v>
       </c>
       <c r="E42" t="str">
-        <v>Potential issue found in CSRF workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F42" t="str">
         <v>src/pages/LiveTracking.tsx</v>
@@ -3162,10 +3162,10 @@
         <v>/tracking</v>
       </c>
       <c r="H42" t="str">
-        <v>Review the CSRF design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I42" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="43">
@@ -3240,7 +3240,7 @@
         <v>Automated assessment item for command injection coverage.</v>
       </c>
       <c r="E45" t="str">
-        <v>Potential issue found in Command Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F45" t="str">
         <v>src/pages/LandingPage.tsx</v>
@@ -3249,10 +3249,10 @@
         <v>/</v>
       </c>
       <c r="H45" t="str">
-        <v>Review the Command Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I45" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="46">
@@ -3281,7 +3281,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I46" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="47">
@@ -3310,7 +3310,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I47" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="48">
@@ -3327,7 +3327,7 @@
         <v>Automated assessment item for secrets coverage.</v>
       </c>
       <c r="E48" t="str">
-        <v>Potential issue found in Secrets workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F48" t="str">
         <v>src/pages/EmergencyContacts.tsx</v>
@@ -3336,10 +3336,10 @@
         <v>/contacts</v>
       </c>
       <c r="H48" t="str">
-        <v>Review the Secrets design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I48" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="49">
@@ -3414,7 +3414,7 @@
         <v>Automated assessment item for sensitive data coverage.</v>
       </c>
       <c r="E51" t="str">
-        <v>Potential issue found in Sensitive Data workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F51" t="str">
         <v>src/pages/Login.tsx</v>
@@ -3423,10 +3423,10 @@
         <v>/login</v>
       </c>
       <c r="H51" t="str">
-        <v>Review the Sensitive Data design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I51" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="52">
@@ -3455,7 +3455,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I52" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="53">
@@ -3484,7 +3484,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I53" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="54">
@@ -3501,7 +3501,7 @@
         <v>Automated assessment item for csp coverage.</v>
       </c>
       <c r="E54" t="str">
-        <v>Potential issue found in CSP workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F54" t="str">
         <v>src/pages/SendSOS.tsx</v>
@@ -3510,10 +3510,10 @@
         <v>/send-sos</v>
       </c>
       <c r="H54" t="str">
-        <v>Review the CSP design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I54" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="55">
@@ -3582,13 +3582,13 @@
         <v>Dependency Risks</v>
       </c>
       <c r="C57" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D57" t="str">
         <v>Automated assessment item for dependency risks coverage.</v>
       </c>
       <c r="E57" t="str">
-        <v>Potential issue found in Dependency Risks workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F57" t="str">
         <v>src/pages/VolunteerDashboard.tsx</v>
@@ -3597,10 +3597,10 @@
         <v>/volunteer</v>
       </c>
       <c r="H57" t="str">
-        <v>Review the Dependency Risks design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I57" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="58">
@@ -3629,7 +3629,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I58" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="59">
@@ -3658,7 +3658,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I59" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="60">
@@ -3675,7 +3675,7 @@
         <v>Automated assessment item for cryptography coverage.</v>
       </c>
       <c r="E60" t="str">
-        <v>Potential issue found in Cryptography workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F60" t="str">
         <v>src/pages/AdminDashboard.tsx</v>
@@ -3684,10 +3684,10 @@
         <v>/admin</v>
       </c>
       <c r="H60" t="str">
-        <v>Review the Cryptography design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I60" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="61">
@@ -3762,7 +3762,7 @@
         <v>Automated assessment item for accessibility coverage.</v>
       </c>
       <c r="E63" t="str">
-        <v>Potential issue found in Accessibility workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F63" t="str">
         <v>src/pages/Dashboard.tsx</v>
@@ -3771,10 +3771,10 @@
         <v>/dashboard</v>
       </c>
       <c r="H63" t="str">
-        <v>Review the Accessibility design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I63" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="64">
@@ -3803,7 +3803,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I64" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="65">
@@ -3832,7 +3832,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I65" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="66">
@@ -3849,7 +3849,7 @@
         <v>Automated assessment item for rbac coverage.</v>
       </c>
       <c r="E66" t="str">
-        <v>Potential issue found in RBAC workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F66" t="str">
         <v>src/pages/UserProfile.tsx</v>
@@ -3858,10 +3858,10 @@
         <v>/profile</v>
       </c>
       <c r="H66" t="str">
-        <v>Review the RBAC design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I66" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="67">
@@ -3936,7 +3936,7 @@
         <v>Automated assessment item for idor coverage.</v>
       </c>
       <c r="E69" t="str">
-        <v>Potential issue found in IDOR workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F69" t="str">
         <v>src/pages/Settings.tsx</v>
@@ -3945,10 +3945,10 @@
         <v>/settings</v>
       </c>
       <c r="H69" t="str">
-        <v>Review the IDOR design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I69" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="70">
@@ -3977,7 +3977,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I70" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="71">
@@ -4006,7 +4006,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I71" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="72">
@@ -4017,13 +4017,13 @@
         <v>XSS</v>
       </c>
       <c r="C72" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D72" t="str">
         <v>Automated assessment item for xss coverage.</v>
       </c>
       <c r="E72" t="str">
-        <v>Potential issue found in XSS workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F72" t="str">
         <v>src/App.tsx</v>
@@ -4032,10 +4032,10 @@
         <v>*</v>
       </c>
       <c r="H72" t="str">
-        <v>Review the XSS design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I72" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="73">
@@ -4110,7 +4110,7 @@
         <v>Automated assessment item for xxe coverage.</v>
       </c>
       <c r="E75" t="str">
-        <v>Potential issue found in XXE workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F75" t="str">
         <v>src/pages/EmergencyChat.tsx</v>
@@ -4119,10 +4119,10 @@
         <v>/chat</v>
       </c>
       <c r="H75" t="str">
-        <v>Review the XXE design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I75" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="76">
@@ -4151,7 +4151,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I76" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="77">
@@ -4180,7 +4180,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I77" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="78">
@@ -4197,7 +4197,7 @@
         <v>Automated assessment item for file upload coverage.</v>
       </c>
       <c r="E78" t="str">
-        <v>Potential issue found in File Upload workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F78" t="str">
         <v>src/pages/EmergencyHistory.tsx</v>
@@ -4206,10 +4206,10 @@
         <v>/history</v>
       </c>
       <c r="H78" t="str">
-        <v>Review the File Upload design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I78" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="79">
@@ -4284,7 +4284,7 @@
         <v>Automated assessment item for logging coverage.</v>
       </c>
       <c r="E81" t="str">
-        <v>Potential issue found in Logging workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F81" t="str">
         <v>src/pages/Registration.tsx</v>
@@ -4293,10 +4293,10 @@
         <v>/register</v>
       </c>
       <c r="H81" t="str">
-        <v>Review the Logging design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I81" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="82">
@@ -4325,7 +4325,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I82" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="83">
@@ -4354,7 +4354,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I83" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="84">
@@ -4371,7 +4371,7 @@
         <v>Automated assessment item for cors coverage.</v>
       </c>
       <c r="E84" t="str">
-        <v>Potential issue found in CORS workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F84" t="str">
         <v>src/pages/LiveTracking.tsx</v>
@@ -4380,10 +4380,10 @@
         <v>/tracking</v>
       </c>
       <c r="H84" t="str">
-        <v>Review the CORS design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I84" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="85">
@@ -4452,13 +4452,13 @@
         <v>Rate Limiting</v>
       </c>
       <c r="C87" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D87" t="str">
         <v>Automated assessment item for rate limiting coverage.</v>
       </c>
       <c r="E87" t="str">
-        <v>Potential issue found in Rate Limiting workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F87" t="str">
         <v>src/pages/LandingPage.tsx</v>
@@ -4467,10 +4467,10 @@
         <v>/</v>
       </c>
       <c r="H87" t="str">
-        <v>Review the Rate Limiting design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I87" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="88">
@@ -4499,7 +4499,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I88" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="89">
@@ -4528,7 +4528,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I89" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="90">
@@ -4545,7 +4545,7 @@
         <v>Automated assessment item for business logic coverage.</v>
       </c>
       <c r="E90" t="str">
-        <v>Potential issue found in Business Logic workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F90" t="str">
         <v>src/pages/EmergencyContacts.tsx</v>
@@ -4554,10 +4554,10 @@
         <v>/contacts</v>
       </c>
       <c r="H90" t="str">
-        <v>Review the Business Logic design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I90" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="91">
@@ -4632,7 +4632,7 @@
         <v>Automated assessment item for performance coverage.</v>
       </c>
       <c r="E93" t="str">
-        <v>Potential issue found in Performance workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F93" t="str">
         <v>src/pages/Login.tsx</v>
@@ -4641,10 +4641,10 @@
         <v>/login</v>
       </c>
       <c r="H93" t="str">
-        <v>Review the Performance design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I93" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="94">
@@ -4673,7 +4673,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I94" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="95">
@@ -4702,7 +4702,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I95" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="96">
@@ -4719,7 +4719,7 @@
         <v>Automated assessment item for authorization coverage.</v>
       </c>
       <c r="E96" t="str">
-        <v>Potential issue found in Authorization workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F96" t="str">
         <v>src/pages/SendSOS.tsx</v>
@@ -4728,10 +4728,10 @@
         <v>/send-sos</v>
       </c>
       <c r="H96" t="str">
-        <v>Review the Authorization design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I96" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="97">
@@ -4806,7 +4806,7 @@
         <v>Automated assessment item for session coverage.</v>
       </c>
       <c r="E99" t="str">
-        <v>Potential issue found in Session workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F99" t="str">
         <v>src/pages/VolunteerDashboard.tsx</v>
@@ -4815,10 +4815,10 @@
         <v>/volunteer</v>
       </c>
       <c r="H99" t="str">
-        <v>Review the Session design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I99" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="100">
@@ -4847,7 +4847,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I100" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="101">
@@ -4876,7 +4876,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I101" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="102">
@@ -4887,13 +4887,13 @@
         <v>NoSQL Injection</v>
       </c>
       <c r="C102" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D102" t="str">
         <v>Automated assessment item for nosql injection coverage.</v>
       </c>
       <c r="E102" t="str">
-        <v>Potential issue found in NoSQL Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F102" t="str">
         <v>src/pages/AdminDashboard.tsx</v>
@@ -4902,10 +4902,10 @@
         <v>/admin</v>
       </c>
       <c r="H102" t="str">
-        <v>Review the NoSQL Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I102" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="103">
@@ -4980,7 +4980,7 @@
         <v>Automated assessment item for ssrf coverage.</v>
       </c>
       <c r="E105" t="str">
-        <v>Potential issue found in SSRF workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F105" t="str">
         <v>src/pages/Dashboard.tsx</v>
@@ -4989,10 +4989,10 @@
         <v>/dashboard</v>
       </c>
       <c r="H105" t="str">
-        <v>Review the SSRF design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I105" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="106">
@@ -5021,7 +5021,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I106" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="107">
@@ -5050,7 +5050,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I107" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="108">
@@ -5067,7 +5067,7 @@
         <v>Automated assessment item for path traversal coverage.</v>
       </c>
       <c r="E108" t="str">
-        <v>Potential issue found in Path Traversal workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F108" t="str">
         <v>src/pages/UserProfile.tsx</v>
@@ -5076,10 +5076,10 @@
         <v>/profile</v>
       </c>
       <c r="H108" t="str">
-        <v>Review the Path Traversal design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I108" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="109">
@@ -5154,7 +5154,7 @@
         <v>Automated assessment item for api keys coverage.</v>
       </c>
       <c r="E111" t="str">
-        <v>Potential issue found in API Keys workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F111" t="str">
         <v>src/pages/Settings.tsx</v>
@@ -5163,10 +5163,10 @@
         <v>/settings</v>
       </c>
       <c r="H111" t="str">
-        <v>Review the API Keys design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I111" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="112">
@@ -5195,7 +5195,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I112" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="113">
@@ -5224,7 +5224,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I113" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="114">
@@ -5241,7 +5241,7 @@
         <v>Automated assessment item for security headers coverage.</v>
       </c>
       <c r="E114" t="str">
-        <v>Potential issue found in Security Headers workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F114" t="str">
         <v>src/App.tsx</v>
@@ -5250,10 +5250,10 @@
         <v>*</v>
       </c>
       <c r="H114" t="str">
-        <v>Review the Security Headers design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I114" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="115">
@@ -5322,13 +5322,13 @@
         <v>Cookies</v>
       </c>
       <c r="C117" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D117" t="str">
         <v>Automated assessment item for cookies coverage.</v>
       </c>
       <c r="E117" t="str">
-        <v>Potential issue found in Cookies workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F117" t="str">
         <v>src/pages/EmergencyChat.tsx</v>
@@ -5337,10 +5337,10 @@
         <v>/chat</v>
       </c>
       <c r="H117" t="str">
-        <v>Review the Cookies design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I117" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="118">
@@ -5369,7 +5369,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I118" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="119">
@@ -5398,7 +5398,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I119" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="120">
@@ -5415,7 +5415,7 @@
         <v>Automated assessment item for configuration coverage.</v>
       </c>
       <c r="E120" t="str">
-        <v>Potential issue found in Configuration workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F120" t="str">
         <v>src/pages/EmergencyHistory.tsx</v>
@@ -5424,10 +5424,10 @@
         <v>/history</v>
       </c>
       <c r="H120" t="str">
-        <v>Review the Configuration design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I120" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="121">
@@ -5502,7 +5502,7 @@
         <v>Automated assessment item for input validation coverage.</v>
       </c>
       <c r="E123" t="str">
-        <v>Potential issue found in Input Validation workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F123" t="str">
         <v>src/pages/Registration.tsx</v>
@@ -5511,10 +5511,10 @@
         <v>/register</v>
       </c>
       <c r="H123" t="str">
-        <v>Review the Input Validation design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I123" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="124">
@@ -5543,7 +5543,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I124" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="125">
@@ -5572,7 +5572,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I125" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="126">
@@ -5589,7 +5589,7 @@
         <v>Automated assessment item for authentication coverage.</v>
       </c>
       <c r="E126" t="str">
-        <v>Potential issue found in Authentication workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F126" t="str">
         <v>src/pages/LiveTracking.tsx</v>
@@ -5598,10 +5598,10 @@
         <v>/tracking</v>
       </c>
       <c r="H126" t="str">
-        <v>Review the Authentication design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I126" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="127">
@@ -5676,7 +5676,7 @@
         <v>Automated assessment item for jwt coverage.</v>
       </c>
       <c r="E129" t="str">
-        <v>Potential issue found in JWT workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F129" t="str">
         <v>src/pages/LandingPage.tsx</v>
@@ -5685,10 +5685,10 @@
         <v>/</v>
       </c>
       <c r="H129" t="str">
-        <v>Review the JWT design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I129" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="130">
@@ -5717,7 +5717,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I130" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="131">
@@ -5746,7 +5746,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I131" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="132">
@@ -5757,13 +5757,13 @@
         <v>SQL Injection</v>
       </c>
       <c r="C132" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D132" t="str">
         <v>Automated assessment item for sql injection coverage.</v>
       </c>
       <c r="E132" t="str">
-        <v>Potential issue found in SQL Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F132" t="str">
         <v>src/pages/EmergencyContacts.tsx</v>
@@ -5772,10 +5772,10 @@
         <v>/contacts</v>
       </c>
       <c r="H132" t="str">
-        <v>Review the SQL Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I132" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="133">
@@ -5850,7 +5850,7 @@
         <v>Automated assessment item for csrf coverage.</v>
       </c>
       <c r="E135" t="str">
-        <v>Potential issue found in CSRF workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F135" t="str">
         <v>src/pages/Login.tsx</v>
@@ -5859,10 +5859,10 @@
         <v>/login</v>
       </c>
       <c r="H135" t="str">
-        <v>Review the CSRF design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I135" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="136">
@@ -5891,7 +5891,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I136" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="137">
@@ -5920,7 +5920,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I137" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="138">
@@ -5937,7 +5937,7 @@
         <v>Automated assessment item for command injection coverage.</v>
       </c>
       <c r="E138" t="str">
-        <v>Potential issue found in Command Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F138" t="str">
         <v>src/pages/SendSOS.tsx</v>
@@ -5946,10 +5946,10 @@
         <v>/send-sos</v>
       </c>
       <c r="H138" t="str">
-        <v>Review the Command Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I138" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="139">
@@ -6024,7 +6024,7 @@
         <v>Automated assessment item for secrets coverage.</v>
       </c>
       <c r="E141" t="str">
-        <v>Potential issue found in Secrets workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F141" t="str">
         <v>src/pages/VolunteerDashboard.tsx</v>
@@ -6033,10 +6033,10 @@
         <v>/volunteer</v>
       </c>
       <c r="H141" t="str">
-        <v>Review the Secrets design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I141" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="142">
@@ -6065,7 +6065,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I142" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="143">
@@ -6094,7 +6094,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I143" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="144">
@@ -6111,7 +6111,7 @@
         <v>Automated assessment item for sensitive data coverage.</v>
       </c>
       <c r="E144" t="str">
-        <v>Potential issue found in Sensitive Data workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F144" t="str">
         <v>src/pages/AdminDashboard.tsx</v>
@@ -6120,10 +6120,10 @@
         <v>/admin</v>
       </c>
       <c r="H144" t="str">
-        <v>Review the Sensitive Data design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I144" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="145">
@@ -6192,13 +6192,13 @@
         <v>CSP</v>
       </c>
       <c r="C147" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D147" t="str">
         <v>Automated assessment item for csp coverage.</v>
       </c>
       <c r="E147" t="str">
-        <v>Potential issue found in CSP workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F147" t="str">
         <v>src/pages/Dashboard.tsx</v>
@@ -6207,10 +6207,10 @@
         <v>/dashboard</v>
       </c>
       <c r="H147" t="str">
-        <v>Review the CSP design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I147" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="148">
@@ -6239,7 +6239,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I148" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="149">
@@ -6268,7 +6268,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I149" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="150">
@@ -6285,7 +6285,7 @@
         <v>Automated assessment item for dependency risks coverage.</v>
       </c>
       <c r="E150" t="str">
-        <v>Potential issue found in Dependency Risks workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F150" t="str">
         <v>src/pages/UserProfile.tsx</v>
@@ -6294,10 +6294,10 @@
         <v>/profile</v>
       </c>
       <c r="H150" t="str">
-        <v>Review the Dependency Risks design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I150" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="151">
@@ -6372,7 +6372,7 @@
         <v>Automated assessment item for cryptography coverage.</v>
       </c>
       <c r="E153" t="str">
-        <v>Potential issue found in Cryptography workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F153" t="str">
         <v>src/pages/Settings.tsx</v>
@@ -6381,10 +6381,10 @@
         <v>/settings</v>
       </c>
       <c r="H153" t="str">
-        <v>Review the Cryptography design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I153" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="154">
@@ -6413,7 +6413,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I154" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="155">
@@ -6442,7 +6442,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I155" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="156">
@@ -6459,7 +6459,7 @@
         <v>Automated assessment item for accessibility coverage.</v>
       </c>
       <c r="E156" t="str">
-        <v>Potential issue found in Accessibility workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F156" t="str">
         <v>src/App.tsx</v>
@@ -6468,10 +6468,10 @@
         <v>*</v>
       </c>
       <c r="H156" t="str">
-        <v>Review the Accessibility design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I156" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="157">
@@ -6546,7 +6546,7 @@
         <v>Automated assessment item for rbac coverage.</v>
       </c>
       <c r="E159" t="str">
-        <v>Potential issue found in RBAC workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F159" t="str">
         <v>src/pages/EmergencyChat.tsx</v>
@@ -6555,10 +6555,10 @@
         <v>/chat</v>
       </c>
       <c r="H159" t="str">
-        <v>Review the RBAC design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I159" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="160">
@@ -6587,7 +6587,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I160" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="161">
@@ -6616,7 +6616,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I161" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="162">
@@ -6627,13 +6627,13 @@
         <v>IDOR</v>
       </c>
       <c r="C162" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D162" t="str">
         <v>Automated assessment item for idor coverage.</v>
       </c>
       <c r="E162" t="str">
-        <v>Potential issue found in IDOR workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F162" t="str">
         <v>src/pages/EmergencyHistory.tsx</v>
@@ -6642,10 +6642,10 @@
         <v>/history</v>
       </c>
       <c r="H162" t="str">
-        <v>Review the IDOR design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I162" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="163">
@@ -6720,7 +6720,7 @@
         <v>Automated assessment item for xss coverage.</v>
       </c>
       <c r="E165" t="str">
-        <v>Potential issue found in XSS workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F165" t="str">
         <v>src/pages/Registration.tsx</v>
@@ -6729,10 +6729,10 @@
         <v>/register</v>
       </c>
       <c r="H165" t="str">
-        <v>Review the XSS design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I165" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="166">
@@ -6761,7 +6761,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I166" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="167">
@@ -6790,7 +6790,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I167" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="168">
@@ -6807,7 +6807,7 @@
         <v>Automated assessment item for xxe coverage.</v>
       </c>
       <c r="E168" t="str">
-        <v>Potential issue found in XXE workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F168" t="str">
         <v>src/pages/LiveTracking.tsx</v>
@@ -6816,10 +6816,10 @@
         <v>/tracking</v>
       </c>
       <c r="H168" t="str">
-        <v>Review the XXE design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I168" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="169">
@@ -6894,7 +6894,7 @@
         <v>Automated assessment item for file upload coverage.</v>
       </c>
       <c r="E171" t="str">
-        <v>Potential issue found in File Upload workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F171" t="str">
         <v>src/pages/LandingPage.tsx</v>
@@ -6903,10 +6903,10 @@
         <v>/</v>
       </c>
       <c r="H171" t="str">
-        <v>Review the File Upload design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I171" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="172">
@@ -6935,7 +6935,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I172" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="173">
@@ -6964,7 +6964,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I173" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="174">
@@ -6981,7 +6981,7 @@
         <v>Automated assessment item for logging coverage.</v>
       </c>
       <c r="E174" t="str">
-        <v>Potential issue found in Logging workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F174" t="str">
         <v>src/pages/EmergencyContacts.tsx</v>
@@ -6990,10 +6990,10 @@
         <v>/contacts</v>
       </c>
       <c r="H174" t="str">
-        <v>Review the Logging design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I174" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="175">
@@ -7062,13 +7062,13 @@
         <v>CORS</v>
       </c>
       <c r="C177" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D177" t="str">
         <v>Automated assessment item for cors coverage.</v>
       </c>
       <c r="E177" t="str">
-        <v>Potential issue found in CORS workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F177" t="str">
         <v>src/pages/Login.tsx</v>
@@ -7077,10 +7077,10 @@
         <v>/login</v>
       </c>
       <c r="H177" t="str">
-        <v>Review the CORS design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I177" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="178">
@@ -7109,7 +7109,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I178" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="179">
@@ -7138,7 +7138,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I179" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="180">
@@ -7155,7 +7155,7 @@
         <v>Automated assessment item for rate limiting coverage.</v>
       </c>
       <c r="E180" t="str">
-        <v>Potential issue found in Rate Limiting workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F180" t="str">
         <v>src/pages/SendSOS.tsx</v>
@@ -7164,10 +7164,10 @@
         <v>/send-sos</v>
       </c>
       <c r="H180" t="str">
-        <v>Review the Rate Limiting design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I180" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="181">
@@ -7242,7 +7242,7 @@
         <v>Automated assessment item for business logic coverage.</v>
       </c>
       <c r="E183" t="str">
-        <v>Potential issue found in Business Logic workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F183" t="str">
         <v>src/pages/VolunteerDashboard.tsx</v>
@@ -7251,10 +7251,10 @@
         <v>/volunteer</v>
       </c>
       <c r="H183" t="str">
-        <v>Review the Business Logic design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I183" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="184">
@@ -7283,7 +7283,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I184" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="185">
@@ -7312,7 +7312,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I185" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="186">
@@ -7329,7 +7329,7 @@
         <v>Automated assessment item for performance coverage.</v>
       </c>
       <c r="E186" t="str">
-        <v>Potential issue found in Performance workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F186" t="str">
         <v>src/pages/AdminDashboard.tsx</v>
@@ -7338,10 +7338,10 @@
         <v>/admin</v>
       </c>
       <c r="H186" t="str">
-        <v>Review the Performance design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I186" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="187">
@@ -7416,7 +7416,7 @@
         <v>Automated assessment item for authorization coverage.</v>
       </c>
       <c r="E189" t="str">
-        <v>Potential issue found in Authorization workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F189" t="str">
         <v>src/pages/Dashboard.tsx</v>
@@ -7425,10 +7425,10 @@
         <v>/dashboard</v>
       </c>
       <c r="H189" t="str">
-        <v>Review the Authorization design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I189" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="190">
@@ -7457,7 +7457,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I190" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="191">
@@ -7486,7 +7486,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I191" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="192">
@@ -7497,13 +7497,13 @@
         <v>Session</v>
       </c>
       <c r="C192" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D192" t="str">
         <v>Automated assessment item for session coverage.</v>
       </c>
       <c r="E192" t="str">
-        <v>Potential issue found in Session workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F192" t="str">
         <v>src/pages/UserProfile.tsx</v>
@@ -7512,10 +7512,10 @@
         <v>/profile</v>
       </c>
       <c r="H192" t="str">
-        <v>Review the Session design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I192" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="193">
@@ -7590,7 +7590,7 @@
         <v>Automated assessment item for nosql injection coverage.</v>
       </c>
       <c r="E195" t="str">
-        <v>Potential issue found in NoSQL Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F195" t="str">
         <v>src/pages/Settings.tsx</v>
@@ -7599,10 +7599,10 @@
         <v>/settings</v>
       </c>
       <c r="H195" t="str">
-        <v>Review the NoSQL Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I195" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="196">
@@ -7631,7 +7631,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I196" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="197">
@@ -7660,7 +7660,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I197" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="198">
@@ -7677,7 +7677,7 @@
         <v>Automated assessment item for ssrf coverage.</v>
       </c>
       <c r="E198" t="str">
-        <v>Potential issue found in SSRF workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F198" t="str">
         <v>src/App.tsx</v>
@@ -7686,10 +7686,10 @@
         <v>*</v>
       </c>
       <c r="H198" t="str">
-        <v>Review the SSRF design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I198" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="199">
@@ -7764,7 +7764,7 @@
         <v>Automated assessment item for path traversal coverage.</v>
       </c>
       <c r="E201" t="str">
-        <v>Potential issue found in Path Traversal workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F201" t="str">
         <v>src/pages/EmergencyChat.tsx</v>
@@ -7773,10 +7773,10 @@
         <v>/chat</v>
       </c>
       <c r="H201" t="str">
-        <v>Review the Path Traversal design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I201" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="202">
@@ -7805,7 +7805,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I202" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="203">
@@ -7834,7 +7834,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I203" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="204">
@@ -7851,7 +7851,7 @@
         <v>Automated assessment item for api keys coverage.</v>
       </c>
       <c r="E204" t="str">
-        <v>Potential issue found in API Keys workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F204" t="str">
         <v>src/pages/EmergencyHistory.tsx</v>
@@ -7860,10 +7860,10 @@
         <v>/history</v>
       </c>
       <c r="H204" t="str">
-        <v>Review the API Keys design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I204" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="205">
@@ -7932,13 +7932,13 @@
         <v>Security Headers</v>
       </c>
       <c r="C207" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D207" t="str">
         <v>Automated assessment item for security headers coverage.</v>
       </c>
       <c r="E207" t="str">
-        <v>Potential issue found in Security Headers workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F207" t="str">
         <v>src/pages/Registration.tsx</v>
@@ -7947,10 +7947,10 @@
         <v>/register</v>
       </c>
       <c r="H207" t="str">
-        <v>Review the Security Headers design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I207" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="208">
@@ -7979,7 +7979,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I208" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="209">
@@ -8008,7 +8008,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I209" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="210">
@@ -8025,7 +8025,7 @@
         <v>Automated assessment item for cookies coverage.</v>
       </c>
       <c r="E210" t="str">
-        <v>Potential issue found in Cookies workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F210" t="str">
         <v>src/pages/LiveTracking.tsx</v>
@@ -8034,10 +8034,10 @@
         <v>/tracking</v>
       </c>
       <c r="H210" t="str">
-        <v>Review the Cookies design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I210" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="211">
@@ -8112,7 +8112,7 @@
         <v>Automated assessment item for configuration coverage.</v>
       </c>
       <c r="E213" t="str">
-        <v>Potential issue found in Configuration workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F213" t="str">
         <v>src/pages/LandingPage.tsx</v>
@@ -8121,10 +8121,10 @@
         <v>/</v>
       </c>
       <c r="H213" t="str">
-        <v>Review the Configuration design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I213" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="214">
@@ -8153,7 +8153,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I214" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="215">
@@ -8182,7 +8182,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I215" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="216">
@@ -8199,7 +8199,7 @@
         <v>Automated assessment item for input validation coverage.</v>
       </c>
       <c r="E216" t="str">
-        <v>Potential issue found in Input Validation workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F216" t="str">
         <v>src/pages/EmergencyContacts.tsx</v>
@@ -8208,10 +8208,10 @@
         <v>/contacts</v>
       </c>
       <c r="H216" t="str">
-        <v>Review the Input Validation design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I216" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="217">
@@ -8286,7 +8286,7 @@
         <v>Automated assessment item for authentication coverage.</v>
       </c>
       <c r="E219" t="str">
-        <v>Potential issue found in Authentication workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F219" t="str">
         <v>src/pages/Login.tsx</v>
@@ -8295,10 +8295,10 @@
         <v>/login</v>
       </c>
       <c r="H219" t="str">
-        <v>Review the Authentication design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I219" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="220">
@@ -8327,7 +8327,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I220" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="221">
@@ -8356,7 +8356,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I221" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="222">
@@ -8367,13 +8367,13 @@
         <v>JWT</v>
       </c>
       <c r="C222" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D222" t="str">
         <v>Automated assessment item for jwt coverage.</v>
       </c>
       <c r="E222" t="str">
-        <v>Potential issue found in JWT workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F222" t="str">
         <v>src/pages/SendSOS.tsx</v>
@@ -8382,10 +8382,10 @@
         <v>/send-sos</v>
       </c>
       <c r="H222" t="str">
-        <v>Review the JWT design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I222" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="223">
@@ -8460,7 +8460,7 @@
         <v>Automated assessment item for sql injection coverage.</v>
       </c>
       <c r="E225" t="str">
-        <v>Potential issue found in SQL Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F225" t="str">
         <v>src/pages/VolunteerDashboard.tsx</v>
@@ -8469,10 +8469,10 @@
         <v>/volunteer</v>
       </c>
       <c r="H225" t="str">
-        <v>Review the SQL Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I225" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="226">
@@ -8501,7 +8501,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I226" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="227">
@@ -8530,7 +8530,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I227" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="228">
@@ -8547,7 +8547,7 @@
         <v>Automated assessment item for csrf coverage.</v>
       </c>
       <c r="E228" t="str">
-        <v>Potential issue found in CSRF workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F228" t="str">
         <v>src/pages/AdminDashboard.tsx</v>
@@ -8556,10 +8556,10 @@
         <v>/admin</v>
       </c>
       <c r="H228" t="str">
-        <v>Review the CSRF design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I228" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="229">
@@ -8634,7 +8634,7 @@
         <v>Automated assessment item for command injection coverage.</v>
       </c>
       <c r="E231" t="str">
-        <v>Potential issue found in Command Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F231" t="str">
         <v>src/pages/Dashboard.tsx</v>
@@ -8643,10 +8643,10 @@
         <v>/dashboard</v>
       </c>
       <c r="H231" t="str">
-        <v>Review the Command Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I231" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="232">
@@ -8675,7 +8675,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I232" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="233">
@@ -8704,7 +8704,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I233" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="234">
@@ -8721,7 +8721,7 @@
         <v>Automated assessment item for secrets coverage.</v>
       </c>
       <c r="E234" t="str">
-        <v>Potential issue found in Secrets workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F234" t="str">
         <v>src/pages/UserProfile.tsx</v>
@@ -8730,10 +8730,10 @@
         <v>/profile</v>
       </c>
       <c r="H234" t="str">
-        <v>Review the Secrets design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I234" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="235">
@@ -8802,13 +8802,13 @@
         <v>Sensitive Data</v>
       </c>
       <c r="C237" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D237" t="str">
         <v>Automated assessment item for sensitive data coverage.</v>
       </c>
       <c r="E237" t="str">
-        <v>Potential issue found in Sensitive Data workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F237" t="str">
         <v>src/pages/Settings.tsx</v>
@@ -8817,10 +8817,10 @@
         <v>/settings</v>
       </c>
       <c r="H237" t="str">
-        <v>Review the Sensitive Data design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I237" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="238">
@@ -8849,7 +8849,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I238" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="239">
@@ -8878,7 +8878,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I239" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="240">
@@ -8895,7 +8895,7 @@
         <v>Automated assessment item for csp coverage.</v>
       </c>
       <c r="E240" t="str">
-        <v>Potential issue found in CSP workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F240" t="str">
         <v>src/App.tsx</v>
@@ -8904,10 +8904,10 @@
         <v>*</v>
       </c>
       <c r="H240" t="str">
-        <v>Review the CSP design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I240" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="241">
@@ -8982,7 +8982,7 @@
         <v>Automated assessment item for dependency risks coverage.</v>
       </c>
       <c r="E243" t="str">
-        <v>Potential issue found in Dependency Risks workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F243" t="str">
         <v>src/pages/EmergencyChat.tsx</v>
@@ -8991,10 +8991,10 @@
         <v>/chat</v>
       </c>
       <c r="H243" t="str">
-        <v>Review the Dependency Risks design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I243" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="244">
@@ -9023,7 +9023,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I244" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="245">
@@ -9052,7 +9052,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I245" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="246">
@@ -9069,7 +9069,7 @@
         <v>Automated assessment item for cryptography coverage.</v>
       </c>
       <c r="E246" t="str">
-        <v>Potential issue found in Cryptography workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F246" t="str">
         <v>src/pages/EmergencyHistory.tsx</v>
@@ -9078,10 +9078,10 @@
         <v>/history</v>
       </c>
       <c r="H246" t="str">
-        <v>Review the Cryptography design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I246" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="247">
@@ -9156,7 +9156,7 @@
         <v>Automated assessment item for accessibility coverage.</v>
       </c>
       <c r="E249" t="str">
-        <v>Potential issue found in Accessibility workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F249" t="str">
         <v>src/pages/Registration.tsx</v>
@@ -9165,10 +9165,10 @@
         <v>/register</v>
       </c>
       <c r="H249" t="str">
-        <v>Review the Accessibility design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I249" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="250">
@@ -9197,7 +9197,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I250" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="251">
@@ -9226,7 +9226,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I251" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="252">
@@ -9237,13 +9237,13 @@
         <v>RBAC</v>
       </c>
       <c r="C252" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D252" t="str">
         <v>Automated assessment item for rbac coverage.</v>
       </c>
       <c r="E252" t="str">
-        <v>Potential issue found in RBAC workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F252" t="str">
         <v>src/pages/LiveTracking.tsx</v>
@@ -9252,10 +9252,10 @@
         <v>/tracking</v>
       </c>
       <c r="H252" t="str">
-        <v>Review the RBAC design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I252" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="253">
@@ -9330,7 +9330,7 @@
         <v>Automated assessment item for idor coverage.</v>
       </c>
       <c r="E255" t="str">
-        <v>Potential issue found in IDOR workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F255" t="str">
         <v>src/pages/LandingPage.tsx</v>
@@ -9339,10 +9339,10 @@
         <v>/</v>
       </c>
       <c r="H255" t="str">
-        <v>Review the IDOR design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I255" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="256">
@@ -9371,7 +9371,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I256" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="257">
@@ -9400,7 +9400,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I257" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="258">
@@ -9417,7 +9417,7 @@
         <v>Automated assessment item for xss coverage.</v>
       </c>
       <c r="E258" t="str">
-        <v>Potential issue found in XSS workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F258" t="str">
         <v>src/pages/EmergencyContacts.tsx</v>
@@ -9426,10 +9426,10 @@
         <v>/contacts</v>
       </c>
       <c r="H258" t="str">
-        <v>Review the XSS design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I258" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="259">
@@ -9504,7 +9504,7 @@
         <v>Automated assessment item for xxe coverage.</v>
       </c>
       <c r="E261" t="str">
-        <v>Potential issue found in XXE workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F261" t="str">
         <v>src/pages/Login.tsx</v>
@@ -9513,10 +9513,10 @@
         <v>/login</v>
       </c>
       <c r="H261" t="str">
-        <v>Review the XXE design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I261" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="262">
@@ -9545,7 +9545,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I262" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="263">
@@ -9574,7 +9574,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I263" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="264">
@@ -9591,7 +9591,7 @@
         <v>Automated assessment item for file upload coverage.</v>
       </c>
       <c r="E264" t="str">
-        <v>Potential issue found in File Upload workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F264" t="str">
         <v>src/pages/SendSOS.tsx</v>
@@ -9600,10 +9600,10 @@
         <v>/send-sos</v>
       </c>
       <c r="H264" t="str">
-        <v>Review the File Upload design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I264" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="265">
@@ -9672,13 +9672,13 @@
         <v>Logging</v>
       </c>
       <c r="C267" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D267" t="str">
         <v>Automated assessment item for logging coverage.</v>
       </c>
       <c r="E267" t="str">
-        <v>Potential issue found in Logging workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F267" t="str">
         <v>src/pages/VolunteerDashboard.tsx</v>
@@ -9687,10 +9687,10 @@
         <v>/volunteer</v>
       </c>
       <c r="H267" t="str">
-        <v>Review the Logging design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I267" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="268">
@@ -9719,7 +9719,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I268" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="269">
@@ -9748,7 +9748,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I269" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="270">
@@ -9765,7 +9765,7 @@
         <v>Automated assessment item for cors coverage.</v>
       </c>
       <c r="E270" t="str">
-        <v>Potential issue found in CORS workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F270" t="str">
         <v>src/pages/AdminDashboard.tsx</v>
@@ -9774,10 +9774,10 @@
         <v>/admin</v>
       </c>
       <c r="H270" t="str">
-        <v>Review the CORS design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I270" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="271">
@@ -9852,7 +9852,7 @@
         <v>Automated assessment item for rate limiting coverage.</v>
       </c>
       <c r="E273" t="str">
-        <v>Potential issue found in Rate Limiting workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F273" t="str">
         <v>src/pages/Dashboard.tsx</v>
@@ -9861,10 +9861,10 @@
         <v>/dashboard</v>
       </c>
       <c r="H273" t="str">
-        <v>Review the Rate Limiting design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I273" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="274">
@@ -9893,7 +9893,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I274" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="275">
@@ -9922,7 +9922,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I275" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="276">
@@ -9939,7 +9939,7 @@
         <v>Automated assessment item for business logic coverage.</v>
       </c>
       <c r="E276" t="str">
-        <v>Potential issue found in Business Logic workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F276" t="str">
         <v>src/pages/UserProfile.tsx</v>
@@ -9948,10 +9948,10 @@
         <v>/profile</v>
       </c>
       <c r="H276" t="str">
-        <v>Review the Business Logic design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I276" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="277">
@@ -10026,7 +10026,7 @@
         <v>Automated assessment item for performance coverage.</v>
       </c>
       <c r="E279" t="str">
-        <v>Potential issue found in Performance workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F279" t="str">
         <v>src/pages/Settings.tsx</v>
@@ -10035,10 +10035,10 @@
         <v>/settings</v>
       </c>
       <c r="H279" t="str">
-        <v>Review the Performance design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I279" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="280">
@@ -10067,7 +10067,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I280" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="281">
@@ -10096,7 +10096,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I281" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="282">
@@ -10107,13 +10107,13 @@
         <v>Authorization</v>
       </c>
       <c r="C282" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D282" t="str">
         <v>Automated assessment item for authorization coverage.</v>
       </c>
       <c r="E282" t="str">
-        <v>Potential issue found in Authorization workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F282" t="str">
         <v>src/App.tsx</v>
@@ -10122,10 +10122,10 @@
         <v>*</v>
       </c>
       <c r="H282" t="str">
-        <v>Review the Authorization design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I282" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="283">
@@ -10200,7 +10200,7 @@
         <v>Automated assessment item for session coverage.</v>
       </c>
       <c r="E285" t="str">
-        <v>Potential issue found in Session workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F285" t="str">
         <v>src/pages/EmergencyChat.tsx</v>
@@ -10209,10 +10209,10 @@
         <v>/chat</v>
       </c>
       <c r="H285" t="str">
-        <v>Review the Session design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I285" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="286">
@@ -10241,7 +10241,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I286" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="287">
@@ -10270,7 +10270,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I287" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="288">
@@ -10287,7 +10287,7 @@
         <v>Automated assessment item for nosql injection coverage.</v>
       </c>
       <c r="E288" t="str">
-        <v>Potential issue found in NoSQL Injection workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F288" t="str">
         <v>src/pages/EmergencyHistory.tsx</v>
@@ -10296,10 +10296,10 @@
         <v>/history</v>
       </c>
       <c r="H288" t="str">
-        <v>Review the NoSQL Injection design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I288" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="289">
@@ -10374,7 +10374,7 @@
         <v>Automated assessment item for ssrf coverage.</v>
       </c>
       <c r="E291" t="str">
-        <v>Potential issue found in SSRF workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F291" t="str">
         <v>src/pages/Registration.tsx</v>
@@ -10383,10 +10383,10 @@
         <v>/register</v>
       </c>
       <c r="H291" t="str">
-        <v>Review the SSRF design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I291" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="292">
@@ -10415,7 +10415,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I292" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="293">
@@ -10444,7 +10444,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I293" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="294">
@@ -10461,7 +10461,7 @@
         <v>Automated assessment item for path traversal coverage.</v>
       </c>
       <c r="E294" t="str">
-        <v>Potential issue found in Path Traversal workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F294" t="str">
         <v>src/pages/LiveTracking.tsx</v>
@@ -10470,10 +10470,10 @@
         <v>/tracking</v>
       </c>
       <c r="H294" t="str">
-        <v>Review the Path Traversal design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I294" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="295">
@@ -10542,13 +10542,13 @@
         <v>API Keys</v>
       </c>
       <c r="C297" t="str">
-        <v>MEDIUM</v>
+        <v>LOW</v>
       </c>
       <c r="D297" t="str">
         <v>Automated assessment item for api keys coverage.</v>
       </c>
       <c r="E297" t="str">
-        <v>Potential issue found in API Keys workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F297" t="str">
         <v>src/pages/LandingPage.tsx</v>
@@ -10557,10 +10557,10 @@
         <v>/</v>
       </c>
       <c r="H297" t="str">
-        <v>Review the API Keys design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I297" t="str">
-        <v>FAIL</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="298">
@@ -10589,7 +10589,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I298" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="299">
@@ -10618,7 +10618,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I299" t="str">
-        <v>PASS</v>
+        <v>NOT APPLICABLE</v>
       </c>
     </row>
     <row r="300">
@@ -10635,7 +10635,7 @@
         <v>Automated assessment item for security headers coverage.</v>
       </c>
       <c r="E300" t="str">
-        <v>Potential issue found in Security Headers workflow.</v>
+        <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F300" t="str">
         <v>src/pages/EmergencyContacts.tsx</v>
@@ -10644,10 +10644,10 @@
         <v>/contacts</v>
       </c>
       <c r="H300" t="str">
-        <v>Review the Security Headers design and apply hardened controls.</v>
+        <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I300" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="301">
@@ -10679,9 +10679,2909 @@
         <v>NOT APPLICABLE</v>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>S-301</v>
+      </c>
+      <c r="B302" t="str">
+        <v>CSP</v>
+      </c>
+      <c r="C302" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D302" t="str">
+        <v>Automated assessment item for csp coverage.</v>
+      </c>
+      <c r="E302" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F302" t="str">
+        <v>src/pages/EmergencyHistory.tsx</v>
+      </c>
+      <c r="G302" t="str">
+        <v>/history</v>
+      </c>
+      <c r="H302" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I302" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>S-302</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Cookies</v>
+      </c>
+      <c r="C303" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D303" t="str">
+        <v>Automated assessment item for cookies coverage.</v>
+      </c>
+      <c r="E303" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F303" t="str">
+        <v>src/pages/Login.tsx</v>
+      </c>
+      <c r="G303" t="str">
+        <v>/login</v>
+      </c>
+      <c r="H303" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I303" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>S-303</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Rate Limiting</v>
+      </c>
+      <c r="C304" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D304" t="str">
+        <v>Automated assessment item for rate limiting coverage.</v>
+      </c>
+      <c r="E304" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F304" t="str">
+        <v>src/pages/UserProfile.tsx</v>
+      </c>
+      <c r="G304" t="str">
+        <v>/profile</v>
+      </c>
+      <c r="H304" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I304" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>S-304</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Dependency Risks</v>
+      </c>
+      <c r="C305" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D305" t="str">
+        <v>Automated assessment item for dependency risks coverage.</v>
+      </c>
+      <c r="E305" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F305" t="str">
+        <v>src/pages/Registration.tsx</v>
+      </c>
+      <c r="G305" t="str">
+        <v>/register</v>
+      </c>
+      <c r="H305" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I305" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>S-305</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Configuration</v>
+      </c>
+      <c r="C306" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D306" t="str">
+        <v>Automated assessment item for configuration coverage.</v>
+      </c>
+      <c r="E306" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F306" t="str">
+        <v>src/pages/SendSOS.tsx</v>
+      </c>
+      <c r="G306" t="str">
+        <v>/send-sos</v>
+      </c>
+      <c r="H306" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I306" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>S-306</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Business Logic</v>
+      </c>
+      <c r="C307" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D307" t="str">
+        <v>Automated assessment item for business logic coverage.</v>
+      </c>
+      <c r="E307" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F307" t="str">
+        <v>src/pages/Settings.tsx</v>
+      </c>
+      <c r="G307" t="str">
+        <v>/settings</v>
+      </c>
+      <c r="H307" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I307" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>S-307</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Cryptography</v>
+      </c>
+      <c r="C308" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D308" t="str">
+        <v>Automated assessment item for cryptography coverage.</v>
+      </c>
+      <c r="E308" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F308" t="str">
+        <v>src/pages/LiveTracking.tsx</v>
+      </c>
+      <c r="G308" t="str">
+        <v>/tracking</v>
+      </c>
+      <c r="H308" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I308" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>S-308</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Input Validation</v>
+      </c>
+      <c r="C309" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D309" t="str">
+        <v>Automated assessment item for input validation coverage.</v>
+      </c>
+      <c r="E309" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F309" t="str">
+        <v>src/pages/VolunteerDashboard.tsx</v>
+      </c>
+      <c r="G309" t="str">
+        <v>/volunteer</v>
+      </c>
+      <c r="H309" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I309" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>S-309</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="C310" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D310" t="str">
+        <v>Automated assessment item for performance coverage.</v>
+      </c>
+      <c r="E310" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F310" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="G310" t="str">
+        <v>*</v>
+      </c>
+      <c r="H310" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I310" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>S-310</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Accessibility</v>
+      </c>
+      <c r="C311" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D311" t="str">
+        <v>Automated assessment item for accessibility coverage.</v>
+      </c>
+      <c r="E311" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F311" t="str">
+        <v>src/pages/LandingPage.tsx</v>
+      </c>
+      <c r="G311" t="str">
+        <v>/</v>
+      </c>
+      <c r="H311" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I311" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>S-311</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C312" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D312" t="str">
+        <v>Automated assessment item for authentication coverage.</v>
+      </c>
+      <c r="E312" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F312" t="str">
+        <v>src/pages/AdminDashboard.tsx</v>
+      </c>
+      <c r="G312" t="str">
+        <v>/admin</v>
+      </c>
+      <c r="H312" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I312" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>S-312</v>
+      </c>
+      <c r="B313" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="C313" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D313" t="str">
+        <v>Automated assessment item for authorization coverage.</v>
+      </c>
+      <c r="E313" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F313" t="str">
+        <v>src/pages/EmergencyChat.tsx</v>
+      </c>
+      <c r="G313" t="str">
+        <v>/chat</v>
+      </c>
+      <c r="H313" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I313" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>S-313</v>
+      </c>
+      <c r="B314" t="str">
+        <v>RBAC</v>
+      </c>
+      <c r="C314" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D314" t="str">
+        <v>Automated assessment item for rbac coverage.</v>
+      </c>
+      <c r="E314" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F314" t="str">
+        <v>src/pages/EmergencyContacts.tsx</v>
+      </c>
+      <c r="G314" t="str">
+        <v>/contacts</v>
+      </c>
+      <c r="H314" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I314" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>S-314</v>
+      </c>
+      <c r="B315" t="str">
+        <v>JWT</v>
+      </c>
+      <c r="C315" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D315" t="str">
+        <v>Automated assessment item for jwt coverage.</v>
+      </c>
+      <c r="E315" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F315" t="str">
+        <v>src/pages/Dashboard.tsx</v>
+      </c>
+      <c r="G315" t="str">
+        <v>/dashboard</v>
+      </c>
+      <c r="H315" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I315" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>S-315</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Session</v>
+      </c>
+      <c r="C316" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D316" t="str">
+        <v>Automated assessment item for session coverage.</v>
+      </c>
+      <c r="E316" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F316" t="str">
+        <v>src/pages/EmergencyHistory.tsx</v>
+      </c>
+      <c r="G316" t="str">
+        <v>/history</v>
+      </c>
+      <c r="H316" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I316" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>S-316</v>
+      </c>
+      <c r="B317" t="str">
+        <v>IDOR</v>
+      </c>
+      <c r="C317" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D317" t="str">
+        <v>Automated assessment item for idor coverage.</v>
+      </c>
+      <c r="E317" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F317" t="str">
+        <v>src/pages/Login.tsx</v>
+      </c>
+      <c r="G317" t="str">
+        <v>/login</v>
+      </c>
+      <c r="H317" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I317" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>S-317</v>
+      </c>
+      <c r="B318" t="str">
+        <v>SQL Injection</v>
+      </c>
+      <c r="C318" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D318" t="str">
+        <v>Automated assessment item for sql injection coverage.</v>
+      </c>
+      <c r="E318" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F318" t="str">
+        <v>src/pages/UserProfile.tsx</v>
+      </c>
+      <c r="G318" t="str">
+        <v>/profile</v>
+      </c>
+      <c r="H318" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I318" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>S-318</v>
+      </c>
+      <c r="B319" t="str">
+        <v>NoSQL Injection</v>
+      </c>
+      <c r="C319" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D319" t="str">
+        <v>Automated assessment item for nosql injection coverage.</v>
+      </c>
+      <c r="E319" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F319" t="str">
+        <v>src/pages/Registration.tsx</v>
+      </c>
+      <c r="G319" t="str">
+        <v>/register</v>
+      </c>
+      <c r="H319" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I319" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>S-319</v>
+      </c>
+      <c r="B320" t="str">
+        <v>XSS</v>
+      </c>
+      <c r="C320" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D320" t="str">
+        <v>Automated assessment item for xss coverage.</v>
+      </c>
+      <c r="E320" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F320" t="str">
+        <v>src/pages/SendSOS.tsx</v>
+      </c>
+      <c r="G320" t="str">
+        <v>/send-sos</v>
+      </c>
+      <c r="H320" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I320" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>S-320</v>
+      </c>
+      <c r="B321" t="str">
+        <v>CSRF</v>
+      </c>
+      <c r="C321" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D321" t="str">
+        <v>Automated assessment item for csrf coverage.</v>
+      </c>
+      <c r="E321" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F321" t="str">
+        <v>src/pages/Settings.tsx</v>
+      </c>
+      <c r="G321" t="str">
+        <v>/settings</v>
+      </c>
+      <c r="H321" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I321" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>S-321</v>
+      </c>
+      <c r="B322" t="str">
+        <v>SSRF</v>
+      </c>
+      <c r="C322" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D322" t="str">
+        <v>Automated assessment item for ssrf coverage.</v>
+      </c>
+      <c r="E322" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F322" t="str">
+        <v>src/pages/LiveTracking.tsx</v>
+      </c>
+      <c r="G322" t="str">
+        <v>/tracking</v>
+      </c>
+      <c r="H322" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I322" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>S-322</v>
+      </c>
+      <c r="B323" t="str">
+        <v>XXE</v>
+      </c>
+      <c r="C323" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D323" t="str">
+        <v>Automated assessment item for xxe coverage.</v>
+      </c>
+      <c r="E323" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F323" t="str">
+        <v>src/pages/VolunteerDashboard.tsx</v>
+      </c>
+      <c r="G323" t="str">
+        <v>/volunteer</v>
+      </c>
+      <c r="H323" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I323" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>S-323</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Command Injection</v>
+      </c>
+      <c r="C324" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D324" t="str">
+        <v>Automated assessment item for command injection coverage.</v>
+      </c>
+      <c r="E324" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F324" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="G324" t="str">
+        <v>*</v>
+      </c>
+      <c r="H324" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I324" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>S-324</v>
+      </c>
+      <c r="B325" t="str">
+        <v>Path Traversal</v>
+      </c>
+      <c r="C325" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D325" t="str">
+        <v>Automated assessment item for path traversal coverage.</v>
+      </c>
+      <c r="E325" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F325" t="str">
+        <v>src/pages/LandingPage.tsx</v>
+      </c>
+      <c r="G325" t="str">
+        <v>/</v>
+      </c>
+      <c r="H325" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I325" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>S-325</v>
+      </c>
+      <c r="B326" t="str">
+        <v>File Upload</v>
+      </c>
+      <c r="C326" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D326" t="str">
+        <v>Automated assessment item for file upload coverage.</v>
+      </c>
+      <c r="E326" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F326" t="str">
+        <v>src/pages/AdminDashboard.tsx</v>
+      </c>
+      <c r="G326" t="str">
+        <v>/admin</v>
+      </c>
+      <c r="H326" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I326" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>S-326</v>
+      </c>
+      <c r="B327" t="str">
+        <v>Secrets</v>
+      </c>
+      <c r="C327" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D327" t="str">
+        <v>Automated assessment item for secrets coverage.</v>
+      </c>
+      <c r="E327" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F327" t="str">
+        <v>src/pages/EmergencyChat.tsx</v>
+      </c>
+      <c r="G327" t="str">
+        <v>/chat</v>
+      </c>
+      <c r="H327" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I327" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>S-327</v>
+      </c>
+      <c r="B328" t="str">
+        <v>API Keys</v>
+      </c>
+      <c r="C328" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D328" t="str">
+        <v>Automated assessment item for api keys coverage.</v>
+      </c>
+      <c r="E328" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F328" t="str">
+        <v>src/pages/EmergencyContacts.tsx</v>
+      </c>
+      <c r="G328" t="str">
+        <v>/contacts</v>
+      </c>
+      <c r="H328" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I328" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>S-328</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Logging</v>
+      </c>
+      <c r="C329" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D329" t="str">
+        <v>Automated assessment item for logging coverage.</v>
+      </c>
+      <c r="E329" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F329" t="str">
+        <v>src/pages/Dashboard.tsx</v>
+      </c>
+      <c r="G329" t="str">
+        <v>/dashboard</v>
+      </c>
+      <c r="H329" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I329" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>S-329</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Sensitive Data</v>
+      </c>
+      <c r="C330" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D330" t="str">
+        <v>Automated assessment item for sensitive data coverage.</v>
+      </c>
+      <c r="E330" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F330" t="str">
+        <v>src/pages/EmergencyHistory.tsx</v>
+      </c>
+      <c r="G330" t="str">
+        <v>/history</v>
+      </c>
+      <c r="H330" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I330" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>S-330</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Security Headers</v>
+      </c>
+      <c r="C331" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D331" t="str">
+        <v>Automated assessment item for security headers coverage.</v>
+      </c>
+      <c r="E331" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F331" t="str">
+        <v>src/pages/Login.tsx</v>
+      </c>
+      <c r="G331" t="str">
+        <v>/login</v>
+      </c>
+      <c r="H331" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I331" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>S-331</v>
+      </c>
+      <c r="B332" t="str">
+        <v>CORS</v>
+      </c>
+      <c r="C332" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D332" t="str">
+        <v>Automated assessment item for cors coverage.</v>
+      </c>
+      <c r="E332" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F332" t="str">
+        <v>src/pages/UserProfile.tsx</v>
+      </c>
+      <c r="G332" t="str">
+        <v>/profile</v>
+      </c>
+      <c r="H332" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I332" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>S-332</v>
+      </c>
+      <c r="B333" t="str">
+        <v>CSP</v>
+      </c>
+      <c r="C333" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D333" t="str">
+        <v>Automated assessment item for csp coverage.</v>
+      </c>
+      <c r="E333" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F333" t="str">
+        <v>src/pages/Registration.tsx</v>
+      </c>
+      <c r="G333" t="str">
+        <v>/register</v>
+      </c>
+      <c r="H333" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I333" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>S-333</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Cookies</v>
+      </c>
+      <c r="C334" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D334" t="str">
+        <v>Automated assessment item for cookies coverage.</v>
+      </c>
+      <c r="E334" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F334" t="str">
+        <v>src/pages/SendSOS.tsx</v>
+      </c>
+      <c r="G334" t="str">
+        <v>/send-sos</v>
+      </c>
+      <c r="H334" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I334" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>S-334</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Rate Limiting</v>
+      </c>
+      <c r="C335" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D335" t="str">
+        <v>Automated assessment item for rate limiting coverage.</v>
+      </c>
+      <c r="E335" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F335" t="str">
+        <v>src/pages/Settings.tsx</v>
+      </c>
+      <c r="G335" t="str">
+        <v>/settings</v>
+      </c>
+      <c r="H335" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I335" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>S-335</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Dependency Risks</v>
+      </c>
+      <c r="C336" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D336" t="str">
+        <v>Automated assessment item for dependency risks coverage.</v>
+      </c>
+      <c r="E336" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F336" t="str">
+        <v>src/pages/LiveTracking.tsx</v>
+      </c>
+      <c r="G336" t="str">
+        <v>/tracking</v>
+      </c>
+      <c r="H336" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I336" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>S-336</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Configuration</v>
+      </c>
+      <c r="C337" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D337" t="str">
+        <v>Automated assessment item for configuration coverage.</v>
+      </c>
+      <c r="E337" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F337" t="str">
+        <v>src/pages/VolunteerDashboard.tsx</v>
+      </c>
+      <c r="G337" t="str">
+        <v>/volunteer</v>
+      </c>
+      <c r="H337" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I337" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>S-337</v>
+      </c>
+      <c r="B338" t="str">
+        <v>Business Logic</v>
+      </c>
+      <c r="C338" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D338" t="str">
+        <v>Automated assessment item for business logic coverage.</v>
+      </c>
+      <c r="E338" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F338" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="G338" t="str">
+        <v>*</v>
+      </c>
+      <c r="H338" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I338" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>S-338</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Cryptography</v>
+      </c>
+      <c r="C339" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D339" t="str">
+        <v>Automated assessment item for cryptography coverage.</v>
+      </c>
+      <c r="E339" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F339" t="str">
+        <v>src/pages/LandingPage.tsx</v>
+      </c>
+      <c r="G339" t="str">
+        <v>/</v>
+      </c>
+      <c r="H339" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I339" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>S-339</v>
+      </c>
+      <c r="B340" t="str">
+        <v>Input Validation</v>
+      </c>
+      <c r="C340" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D340" t="str">
+        <v>Automated assessment item for input validation coverage.</v>
+      </c>
+      <c r="E340" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F340" t="str">
+        <v>src/pages/AdminDashboard.tsx</v>
+      </c>
+      <c r="G340" t="str">
+        <v>/admin</v>
+      </c>
+      <c r="H340" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I340" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>S-340</v>
+      </c>
+      <c r="B341" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="C341" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D341" t="str">
+        <v>Automated assessment item for performance coverage.</v>
+      </c>
+      <c r="E341" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F341" t="str">
+        <v>src/pages/EmergencyChat.tsx</v>
+      </c>
+      <c r="G341" t="str">
+        <v>/chat</v>
+      </c>
+      <c r="H341" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I341" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>S-341</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Accessibility</v>
+      </c>
+      <c r="C342" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D342" t="str">
+        <v>Automated assessment item for accessibility coverage.</v>
+      </c>
+      <c r="E342" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F342" t="str">
+        <v>src/pages/EmergencyContacts.tsx</v>
+      </c>
+      <c r="G342" t="str">
+        <v>/contacts</v>
+      </c>
+      <c r="H342" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I342" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>S-342</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C343" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D343" t="str">
+        <v>Automated assessment item for authentication coverage.</v>
+      </c>
+      <c r="E343" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F343" t="str">
+        <v>src/pages/Dashboard.tsx</v>
+      </c>
+      <c r="G343" t="str">
+        <v>/dashboard</v>
+      </c>
+      <c r="H343" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I343" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>S-343</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="C344" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D344" t="str">
+        <v>Automated assessment item for authorization coverage.</v>
+      </c>
+      <c r="E344" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F344" t="str">
+        <v>src/pages/EmergencyHistory.tsx</v>
+      </c>
+      <c r="G344" t="str">
+        <v>/history</v>
+      </c>
+      <c r="H344" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I344" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>S-344</v>
+      </c>
+      <c r="B345" t="str">
+        <v>RBAC</v>
+      </c>
+      <c r="C345" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D345" t="str">
+        <v>Automated assessment item for rbac coverage.</v>
+      </c>
+      <c r="E345" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F345" t="str">
+        <v>src/pages/Login.tsx</v>
+      </c>
+      <c r="G345" t="str">
+        <v>/login</v>
+      </c>
+      <c r="H345" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I345" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>S-345</v>
+      </c>
+      <c r="B346" t="str">
+        <v>JWT</v>
+      </c>
+      <c r="C346" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D346" t="str">
+        <v>Automated assessment item for jwt coverage.</v>
+      </c>
+      <c r="E346" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F346" t="str">
+        <v>src/pages/UserProfile.tsx</v>
+      </c>
+      <c r="G346" t="str">
+        <v>/profile</v>
+      </c>
+      <c r="H346" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I346" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>S-346</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Session</v>
+      </c>
+      <c r="C347" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D347" t="str">
+        <v>Automated assessment item for session coverage.</v>
+      </c>
+      <c r="E347" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F347" t="str">
+        <v>src/pages/Registration.tsx</v>
+      </c>
+      <c r="G347" t="str">
+        <v>/register</v>
+      </c>
+      <c r="H347" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I347" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>S-347</v>
+      </c>
+      <c r="B348" t="str">
+        <v>IDOR</v>
+      </c>
+      <c r="C348" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D348" t="str">
+        <v>Automated assessment item for idor coverage.</v>
+      </c>
+      <c r="E348" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F348" t="str">
+        <v>src/pages/SendSOS.tsx</v>
+      </c>
+      <c r="G348" t="str">
+        <v>/send-sos</v>
+      </c>
+      <c r="H348" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I348" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>S-348</v>
+      </c>
+      <c r="B349" t="str">
+        <v>SQL Injection</v>
+      </c>
+      <c r="C349" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D349" t="str">
+        <v>Automated assessment item for sql injection coverage.</v>
+      </c>
+      <c r="E349" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F349" t="str">
+        <v>src/pages/Settings.tsx</v>
+      </c>
+      <c r="G349" t="str">
+        <v>/settings</v>
+      </c>
+      <c r="H349" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I349" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>S-349</v>
+      </c>
+      <c r="B350" t="str">
+        <v>NoSQL Injection</v>
+      </c>
+      <c r="C350" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D350" t="str">
+        <v>Automated assessment item for nosql injection coverage.</v>
+      </c>
+      <c r="E350" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F350" t="str">
+        <v>src/pages/LiveTracking.tsx</v>
+      </c>
+      <c r="G350" t="str">
+        <v>/tracking</v>
+      </c>
+      <c r="H350" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I350" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>S-350</v>
+      </c>
+      <c r="B351" t="str">
+        <v>XSS</v>
+      </c>
+      <c r="C351" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D351" t="str">
+        <v>Automated assessment item for xss coverage.</v>
+      </c>
+      <c r="E351" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F351" t="str">
+        <v>src/pages/VolunteerDashboard.tsx</v>
+      </c>
+      <c r="G351" t="str">
+        <v>/volunteer</v>
+      </c>
+      <c r="H351" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I351" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>S-351</v>
+      </c>
+      <c r="B352" t="str">
+        <v>CSRF</v>
+      </c>
+      <c r="C352" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D352" t="str">
+        <v>Automated assessment item for csrf coverage.</v>
+      </c>
+      <c r="E352" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F352" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="G352" t="str">
+        <v>*</v>
+      </c>
+      <c r="H352" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I352" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>S-352</v>
+      </c>
+      <c r="B353" t="str">
+        <v>SSRF</v>
+      </c>
+      <c r="C353" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D353" t="str">
+        <v>Automated assessment item for ssrf coverage.</v>
+      </c>
+      <c r="E353" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F353" t="str">
+        <v>src/pages/LandingPage.tsx</v>
+      </c>
+      <c r="G353" t="str">
+        <v>/</v>
+      </c>
+      <c r="H353" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I353" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>S-353</v>
+      </c>
+      <c r="B354" t="str">
+        <v>XXE</v>
+      </c>
+      <c r="C354" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D354" t="str">
+        <v>Automated assessment item for xxe coverage.</v>
+      </c>
+      <c r="E354" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F354" t="str">
+        <v>src/pages/AdminDashboard.tsx</v>
+      </c>
+      <c r="G354" t="str">
+        <v>/admin</v>
+      </c>
+      <c r="H354" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I354" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>S-354</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Command Injection</v>
+      </c>
+      <c r="C355" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D355" t="str">
+        <v>Automated assessment item for command injection coverage.</v>
+      </c>
+      <c r="E355" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F355" t="str">
+        <v>src/pages/EmergencyChat.tsx</v>
+      </c>
+      <c r="G355" t="str">
+        <v>/chat</v>
+      </c>
+      <c r="H355" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I355" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>S-355</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Path Traversal</v>
+      </c>
+      <c r="C356" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D356" t="str">
+        <v>Automated assessment item for path traversal coverage.</v>
+      </c>
+      <c r="E356" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F356" t="str">
+        <v>src/pages/EmergencyContacts.tsx</v>
+      </c>
+      <c r="G356" t="str">
+        <v>/contacts</v>
+      </c>
+      <c r="H356" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I356" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>S-356</v>
+      </c>
+      <c r="B357" t="str">
+        <v>File Upload</v>
+      </c>
+      <c r="C357" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D357" t="str">
+        <v>Automated assessment item for file upload coverage.</v>
+      </c>
+      <c r="E357" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F357" t="str">
+        <v>src/pages/Dashboard.tsx</v>
+      </c>
+      <c r="G357" t="str">
+        <v>/dashboard</v>
+      </c>
+      <c r="H357" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I357" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>S-357</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Secrets</v>
+      </c>
+      <c r="C358" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D358" t="str">
+        <v>Automated assessment item for secrets coverage.</v>
+      </c>
+      <c r="E358" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F358" t="str">
+        <v>src/pages/EmergencyHistory.tsx</v>
+      </c>
+      <c r="G358" t="str">
+        <v>/history</v>
+      </c>
+      <c r="H358" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I358" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>S-358</v>
+      </c>
+      <c r="B359" t="str">
+        <v>API Keys</v>
+      </c>
+      <c r="C359" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D359" t="str">
+        <v>Automated assessment item for api keys coverage.</v>
+      </c>
+      <c r="E359" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F359" t="str">
+        <v>src/pages/Login.tsx</v>
+      </c>
+      <c r="G359" t="str">
+        <v>/login</v>
+      </c>
+      <c r="H359" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I359" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>S-359</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Logging</v>
+      </c>
+      <c r="C360" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D360" t="str">
+        <v>Automated assessment item for logging coverage.</v>
+      </c>
+      <c r="E360" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F360" t="str">
+        <v>src/pages/UserProfile.tsx</v>
+      </c>
+      <c r="G360" t="str">
+        <v>/profile</v>
+      </c>
+      <c r="H360" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I360" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>S-360</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Sensitive Data</v>
+      </c>
+      <c r="C361" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D361" t="str">
+        <v>Automated assessment item for sensitive data coverage.</v>
+      </c>
+      <c r="E361" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F361" t="str">
+        <v>src/pages/Registration.tsx</v>
+      </c>
+      <c r="G361" t="str">
+        <v>/register</v>
+      </c>
+      <c r="H361" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I361" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>S-361</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Security Headers</v>
+      </c>
+      <c r="C362" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D362" t="str">
+        <v>Automated assessment item for security headers coverage.</v>
+      </c>
+      <c r="E362" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F362" t="str">
+        <v>src/pages/SendSOS.tsx</v>
+      </c>
+      <c r="G362" t="str">
+        <v>/send-sos</v>
+      </c>
+      <c r="H362" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I362" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>S-362</v>
+      </c>
+      <c r="B363" t="str">
+        <v>CORS</v>
+      </c>
+      <c r="C363" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D363" t="str">
+        <v>Automated assessment item for cors coverage.</v>
+      </c>
+      <c r="E363" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F363" t="str">
+        <v>src/pages/Settings.tsx</v>
+      </c>
+      <c r="G363" t="str">
+        <v>/settings</v>
+      </c>
+      <c r="H363" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I363" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>S-363</v>
+      </c>
+      <c r="B364" t="str">
+        <v>CSP</v>
+      </c>
+      <c r="C364" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D364" t="str">
+        <v>Automated assessment item for csp coverage.</v>
+      </c>
+      <c r="E364" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F364" t="str">
+        <v>src/pages/LiveTracking.tsx</v>
+      </c>
+      <c r="G364" t="str">
+        <v>/tracking</v>
+      </c>
+      <c r="H364" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I364" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>S-364</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Cookies</v>
+      </c>
+      <c r="C365" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D365" t="str">
+        <v>Automated assessment item for cookies coverage.</v>
+      </c>
+      <c r="E365" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F365" t="str">
+        <v>src/pages/VolunteerDashboard.tsx</v>
+      </c>
+      <c r="G365" t="str">
+        <v>/volunteer</v>
+      </c>
+      <c r="H365" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I365" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>S-365</v>
+      </c>
+      <c r="B366" t="str">
+        <v>Rate Limiting</v>
+      </c>
+      <c r="C366" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D366" t="str">
+        <v>Automated assessment item for rate limiting coverage.</v>
+      </c>
+      <c r="E366" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F366" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="G366" t="str">
+        <v>*</v>
+      </c>
+      <c r="H366" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I366" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>S-366</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Dependency Risks</v>
+      </c>
+      <c r="C367" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D367" t="str">
+        <v>Automated assessment item for dependency risks coverage.</v>
+      </c>
+      <c r="E367" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F367" t="str">
+        <v>src/pages/LandingPage.tsx</v>
+      </c>
+      <c r="G367" t="str">
+        <v>/</v>
+      </c>
+      <c r="H367" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I367" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>S-367</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Configuration</v>
+      </c>
+      <c r="C368" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D368" t="str">
+        <v>Automated assessment item for configuration coverage.</v>
+      </c>
+      <c r="E368" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F368" t="str">
+        <v>src/pages/AdminDashboard.tsx</v>
+      </c>
+      <c r="G368" t="str">
+        <v>/admin</v>
+      </c>
+      <c r="H368" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I368" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>S-368</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Business Logic</v>
+      </c>
+      <c r="C369" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D369" t="str">
+        <v>Automated assessment item for business logic coverage.</v>
+      </c>
+      <c r="E369" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F369" t="str">
+        <v>src/pages/EmergencyChat.tsx</v>
+      </c>
+      <c r="G369" t="str">
+        <v>/chat</v>
+      </c>
+      <c r="H369" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I369" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>S-369</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Cryptography</v>
+      </c>
+      <c r="C370" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D370" t="str">
+        <v>Automated assessment item for cryptography coverage.</v>
+      </c>
+      <c r="E370" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F370" t="str">
+        <v>src/pages/EmergencyContacts.tsx</v>
+      </c>
+      <c r="G370" t="str">
+        <v>/contacts</v>
+      </c>
+      <c r="H370" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I370" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>S-370</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Input Validation</v>
+      </c>
+      <c r="C371" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D371" t="str">
+        <v>Automated assessment item for input validation coverage.</v>
+      </c>
+      <c r="E371" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F371" t="str">
+        <v>src/pages/Dashboard.tsx</v>
+      </c>
+      <c r="G371" t="str">
+        <v>/dashboard</v>
+      </c>
+      <c r="H371" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I371" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>S-371</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="C372" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D372" t="str">
+        <v>Automated assessment item for performance coverage.</v>
+      </c>
+      <c r="E372" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F372" t="str">
+        <v>src/pages/EmergencyHistory.tsx</v>
+      </c>
+      <c r="G372" t="str">
+        <v>/history</v>
+      </c>
+      <c r="H372" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I372" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>S-372</v>
+      </c>
+      <c r="B373" t="str">
+        <v>Accessibility</v>
+      </c>
+      <c r="C373" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D373" t="str">
+        <v>Automated assessment item for accessibility coverage.</v>
+      </c>
+      <c r="E373" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F373" t="str">
+        <v>src/pages/Login.tsx</v>
+      </c>
+      <c r="G373" t="str">
+        <v>/login</v>
+      </c>
+      <c r="H373" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I373" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>S-373</v>
+      </c>
+      <c r="B374" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C374" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D374" t="str">
+        <v>Automated assessment item for authentication coverage.</v>
+      </c>
+      <c r="E374" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F374" t="str">
+        <v>src/pages/UserProfile.tsx</v>
+      </c>
+      <c r="G374" t="str">
+        <v>/profile</v>
+      </c>
+      <c r="H374" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I374" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>S-374</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="C375" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D375" t="str">
+        <v>Automated assessment item for authorization coverage.</v>
+      </c>
+      <c r="E375" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F375" t="str">
+        <v>src/pages/Registration.tsx</v>
+      </c>
+      <c r="G375" t="str">
+        <v>/register</v>
+      </c>
+      <c r="H375" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I375" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>S-375</v>
+      </c>
+      <c r="B376" t="str">
+        <v>RBAC</v>
+      </c>
+      <c r="C376" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D376" t="str">
+        <v>Automated assessment item for rbac coverage.</v>
+      </c>
+      <c r="E376" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F376" t="str">
+        <v>src/pages/SendSOS.tsx</v>
+      </c>
+      <c r="G376" t="str">
+        <v>/send-sos</v>
+      </c>
+      <c r="H376" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I376" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>S-376</v>
+      </c>
+      <c r="B377" t="str">
+        <v>JWT</v>
+      </c>
+      <c r="C377" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D377" t="str">
+        <v>Automated assessment item for jwt coverage.</v>
+      </c>
+      <c r="E377" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F377" t="str">
+        <v>src/pages/Settings.tsx</v>
+      </c>
+      <c r="G377" t="str">
+        <v>/settings</v>
+      </c>
+      <c r="H377" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I377" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>S-377</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Session</v>
+      </c>
+      <c r="C378" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D378" t="str">
+        <v>Automated assessment item for session coverage.</v>
+      </c>
+      <c r="E378" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F378" t="str">
+        <v>src/pages/LiveTracking.tsx</v>
+      </c>
+      <c r="G378" t="str">
+        <v>/tracking</v>
+      </c>
+      <c r="H378" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I378" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>S-378</v>
+      </c>
+      <c r="B379" t="str">
+        <v>IDOR</v>
+      </c>
+      <c r="C379" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D379" t="str">
+        <v>Automated assessment item for idor coverage.</v>
+      </c>
+      <c r="E379" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F379" t="str">
+        <v>src/pages/VolunteerDashboard.tsx</v>
+      </c>
+      <c r="G379" t="str">
+        <v>/volunteer</v>
+      </c>
+      <c r="H379" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I379" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>S-379</v>
+      </c>
+      <c r="B380" t="str">
+        <v>SQL Injection</v>
+      </c>
+      <c r="C380" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D380" t="str">
+        <v>Automated assessment item for sql injection coverage.</v>
+      </c>
+      <c r="E380" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F380" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="G380" t="str">
+        <v>*</v>
+      </c>
+      <c r="H380" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I380" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>S-380</v>
+      </c>
+      <c r="B381" t="str">
+        <v>NoSQL Injection</v>
+      </c>
+      <c r="C381" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D381" t="str">
+        <v>Automated assessment item for nosql injection coverage.</v>
+      </c>
+      <c r="E381" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F381" t="str">
+        <v>src/pages/LandingPage.tsx</v>
+      </c>
+      <c r="G381" t="str">
+        <v>/</v>
+      </c>
+      <c r="H381" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I381" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>S-381</v>
+      </c>
+      <c r="B382" t="str">
+        <v>XSS</v>
+      </c>
+      <c r="C382" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D382" t="str">
+        <v>Automated assessment item for xss coverage.</v>
+      </c>
+      <c r="E382" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F382" t="str">
+        <v>src/pages/AdminDashboard.tsx</v>
+      </c>
+      <c r="G382" t="str">
+        <v>/admin</v>
+      </c>
+      <c r="H382" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I382" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>S-382</v>
+      </c>
+      <c r="B383" t="str">
+        <v>CSRF</v>
+      </c>
+      <c r="C383" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D383" t="str">
+        <v>Automated assessment item for csrf coverage.</v>
+      </c>
+      <c r="E383" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F383" t="str">
+        <v>src/pages/EmergencyChat.tsx</v>
+      </c>
+      <c r="G383" t="str">
+        <v>/chat</v>
+      </c>
+      <c r="H383" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I383" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>S-383</v>
+      </c>
+      <c r="B384" t="str">
+        <v>SSRF</v>
+      </c>
+      <c r="C384" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D384" t="str">
+        <v>Automated assessment item for ssrf coverage.</v>
+      </c>
+      <c r="E384" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F384" t="str">
+        <v>src/pages/EmergencyContacts.tsx</v>
+      </c>
+      <c r="G384" t="str">
+        <v>/contacts</v>
+      </c>
+      <c r="H384" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I384" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>S-384</v>
+      </c>
+      <c r="B385" t="str">
+        <v>XXE</v>
+      </c>
+      <c r="C385" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D385" t="str">
+        <v>Automated assessment item for xxe coverage.</v>
+      </c>
+      <c r="E385" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F385" t="str">
+        <v>src/pages/Dashboard.tsx</v>
+      </c>
+      <c r="G385" t="str">
+        <v>/dashboard</v>
+      </c>
+      <c r="H385" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I385" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>S-385</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Command Injection</v>
+      </c>
+      <c r="C386" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D386" t="str">
+        <v>Automated assessment item for command injection coverage.</v>
+      </c>
+      <c r="E386" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F386" t="str">
+        <v>src/pages/EmergencyHistory.tsx</v>
+      </c>
+      <c r="G386" t="str">
+        <v>/history</v>
+      </c>
+      <c r="H386" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I386" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>S-386</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Path Traversal</v>
+      </c>
+      <c r="C387" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D387" t="str">
+        <v>Automated assessment item for path traversal coverage.</v>
+      </c>
+      <c r="E387" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F387" t="str">
+        <v>src/pages/Login.tsx</v>
+      </c>
+      <c r="G387" t="str">
+        <v>/login</v>
+      </c>
+      <c r="H387" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I387" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>S-387</v>
+      </c>
+      <c r="B388" t="str">
+        <v>File Upload</v>
+      </c>
+      <c r="C388" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D388" t="str">
+        <v>Automated assessment item for file upload coverage.</v>
+      </c>
+      <c r="E388" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F388" t="str">
+        <v>src/pages/UserProfile.tsx</v>
+      </c>
+      <c r="G388" t="str">
+        <v>/profile</v>
+      </c>
+      <c r="H388" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I388" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>S-388</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Secrets</v>
+      </c>
+      <c r="C389" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D389" t="str">
+        <v>Automated assessment item for secrets coverage.</v>
+      </c>
+      <c r="E389" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F389" t="str">
+        <v>src/pages/Registration.tsx</v>
+      </c>
+      <c r="G389" t="str">
+        <v>/register</v>
+      </c>
+      <c r="H389" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I389" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>S-389</v>
+      </c>
+      <c r="B390" t="str">
+        <v>API Keys</v>
+      </c>
+      <c r="C390" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D390" t="str">
+        <v>Automated assessment item for api keys coverage.</v>
+      </c>
+      <c r="E390" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F390" t="str">
+        <v>src/pages/SendSOS.tsx</v>
+      </c>
+      <c r="G390" t="str">
+        <v>/send-sos</v>
+      </c>
+      <c r="H390" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I390" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>S-390</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Logging</v>
+      </c>
+      <c r="C391" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D391" t="str">
+        <v>Automated assessment item for logging coverage.</v>
+      </c>
+      <c r="E391" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F391" t="str">
+        <v>src/pages/Settings.tsx</v>
+      </c>
+      <c r="G391" t="str">
+        <v>/settings</v>
+      </c>
+      <c r="H391" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I391" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>S-391</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Sensitive Data</v>
+      </c>
+      <c r="C392" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D392" t="str">
+        <v>Automated assessment item for sensitive data coverage.</v>
+      </c>
+      <c r="E392" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F392" t="str">
+        <v>src/pages/LiveTracking.tsx</v>
+      </c>
+      <c r="G392" t="str">
+        <v>/tracking</v>
+      </c>
+      <c r="H392" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I392" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>S-392</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Security Headers</v>
+      </c>
+      <c r="C393" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D393" t="str">
+        <v>Automated assessment item for security headers coverage.</v>
+      </c>
+      <c r="E393" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F393" t="str">
+        <v>src/pages/VolunteerDashboard.tsx</v>
+      </c>
+      <c r="G393" t="str">
+        <v>/volunteer</v>
+      </c>
+      <c r="H393" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I393" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>S-393</v>
+      </c>
+      <c r="B394" t="str">
+        <v>CORS</v>
+      </c>
+      <c r="C394" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D394" t="str">
+        <v>Automated assessment item for cors coverage.</v>
+      </c>
+      <c r="E394" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F394" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="G394" t="str">
+        <v>*</v>
+      </c>
+      <c r="H394" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I394" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>S-394</v>
+      </c>
+      <c r="B395" t="str">
+        <v>CSP</v>
+      </c>
+      <c r="C395" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D395" t="str">
+        <v>Automated assessment item for csp coverage.</v>
+      </c>
+      <c r="E395" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F395" t="str">
+        <v>src/pages/LandingPage.tsx</v>
+      </c>
+      <c r="G395" t="str">
+        <v>/</v>
+      </c>
+      <c r="H395" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I395" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>S-395</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Cookies</v>
+      </c>
+      <c r="C396" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D396" t="str">
+        <v>Automated assessment item for cookies coverage.</v>
+      </c>
+      <c r="E396" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F396" t="str">
+        <v>src/pages/AdminDashboard.tsx</v>
+      </c>
+      <c r="G396" t="str">
+        <v>/admin</v>
+      </c>
+      <c r="H396" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I396" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>S-396</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Rate Limiting</v>
+      </c>
+      <c r="C397" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D397" t="str">
+        <v>Automated assessment item for rate limiting coverage.</v>
+      </c>
+      <c r="E397" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F397" t="str">
+        <v>src/pages/EmergencyChat.tsx</v>
+      </c>
+      <c r="G397" t="str">
+        <v>/chat</v>
+      </c>
+      <c r="H397" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I397" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>S-397</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Dependency Risks</v>
+      </c>
+      <c r="C398" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D398" t="str">
+        <v>Automated assessment item for dependency risks coverage.</v>
+      </c>
+      <c r="E398" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F398" t="str">
+        <v>src/pages/EmergencyContacts.tsx</v>
+      </c>
+      <c r="G398" t="str">
+        <v>/contacts</v>
+      </c>
+      <c r="H398" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I398" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>S-398</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Configuration</v>
+      </c>
+      <c r="C399" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D399" t="str">
+        <v>Automated assessment item for configuration coverage.</v>
+      </c>
+      <c r="E399" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F399" t="str">
+        <v>src/pages/Dashboard.tsx</v>
+      </c>
+      <c r="G399" t="str">
+        <v>/dashboard</v>
+      </c>
+      <c r="H399" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I399" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>S-399</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Business Logic</v>
+      </c>
+      <c r="C400" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D400" t="str">
+        <v>Automated assessment item for business logic coverage.</v>
+      </c>
+      <c r="E400" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F400" t="str">
+        <v>src/pages/EmergencyHistory.tsx</v>
+      </c>
+      <c r="G400" t="str">
+        <v>/history</v>
+      </c>
+      <c r="H400" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I400" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>S-400</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Cryptography</v>
+      </c>
+      <c r="C401" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="D401" t="str">
+        <v>Automated assessment item for cryptography coverage.</v>
+      </c>
+      <c r="E401" t="str">
+        <v>No evidence of risky behavior detected during static assessment.</v>
+      </c>
+      <c r="F401" t="str">
+        <v>src/pages/Login.tsx</v>
+      </c>
+      <c r="G401" t="str">
+        <v>/login</v>
+      </c>
+      <c r="H401" t="str">
+        <v>Maintain current implementation and monitor for future issues.</v>
+      </c>
+      <c r="I401" t="str">
+        <v>NOT APPLICABLE</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I301"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I401"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/Security Findings.xlsx
+++ b/reports/Security Findings.xlsx
@@ -414,7 +414,7 @@
         <v>Generated At</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-31T11:19:36.539Z</v>
+        <v>2026-08-01T10:50:47.052Z</v>
       </c>
     </row>
     <row r="3">
@@ -680,10 +680,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F8" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G8" t="str">
-        <v>/history</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H8" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -709,10 +709,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F9" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G9" t="str">
-        <v>/login</v>
+        <v>/history</v>
       </c>
       <c r="H9" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -738,10 +738,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F10" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G10" t="str">
-        <v>/profile</v>
+        <v>/login</v>
       </c>
       <c r="H10" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -767,10 +767,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F11" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G11" t="str">
-        <v>/register</v>
+        <v>/profile</v>
       </c>
       <c r="H11" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -796,10 +796,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F12" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G12" t="str">
-        <v>/send-sos</v>
+        <v>/register</v>
       </c>
       <c r="H12" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -825,10 +825,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F13" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G13" t="str">
-        <v>/settings</v>
+        <v>/reset-password</v>
       </c>
       <c r="H13" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -854,10 +854,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F14" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G14" t="str">
-        <v>/tracking</v>
+        <v>/send-sos</v>
       </c>
       <c r="H14" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -883,10 +883,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F15" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G15" t="str">
-        <v>/volunteer</v>
+        <v>/settings</v>
       </c>
       <c r="H15" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -912,10 +912,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F16" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G16" t="str">
-        <v>*</v>
+        <v>/tracking</v>
       </c>
       <c r="H16" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -941,10 +941,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F17" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G17" t="str">
-        <v>/</v>
+        <v>/verify-email</v>
       </c>
       <c r="H17" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -970,10 +970,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F18" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G18" t="str">
-        <v>/admin</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H18" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -999,10 +999,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F19" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G19" t="str">
-        <v>/chat</v>
+        <v>/volunteer</v>
       </c>
       <c r="H19" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1028,10 +1028,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F20" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G20" t="str">
-        <v>/contacts</v>
+        <v>*</v>
       </c>
       <c r="H20" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1057,10 +1057,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F21" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G21" t="str">
-        <v>/dashboard</v>
+        <v>/</v>
       </c>
       <c r="H21" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1086,10 +1086,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F22" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G22" t="str">
-        <v>/history</v>
+        <v>/admin</v>
       </c>
       <c r="H22" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1115,10 +1115,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F23" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G23" t="str">
-        <v>/login</v>
+        <v>/chat</v>
       </c>
       <c r="H23" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1144,10 +1144,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F24" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G24" t="str">
-        <v>/profile</v>
+        <v>/contacts</v>
       </c>
       <c r="H24" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1173,10 +1173,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F25" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G25" t="str">
-        <v>/register</v>
+        <v>/dashboard</v>
       </c>
       <c r="H25" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1202,10 +1202,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F26" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G26" t="str">
-        <v>/send-sos</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H26" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1231,10 +1231,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F27" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G27" t="str">
-        <v>/settings</v>
+        <v>/history</v>
       </c>
       <c r="H27" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1260,10 +1260,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F28" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G28" t="str">
-        <v>/tracking</v>
+        <v>/login</v>
       </c>
       <c r="H28" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1289,10 +1289,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F29" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G29" t="str">
-        <v>/volunteer</v>
+        <v>/profile</v>
       </c>
       <c r="H29" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1318,10 +1318,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F30" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G30" t="str">
-        <v>*</v>
+        <v>/register</v>
       </c>
       <c r="H30" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1347,10 +1347,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F31" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G31" t="str">
-        <v>/</v>
+        <v>/reset-password</v>
       </c>
       <c r="H31" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1376,10 +1376,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F32" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G32" t="str">
-        <v>/admin</v>
+        <v>/send-sos</v>
       </c>
       <c r="H32" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1405,10 +1405,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F33" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G33" t="str">
-        <v>/chat</v>
+        <v>/settings</v>
       </c>
       <c r="H33" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1434,10 +1434,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F34" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G34" t="str">
-        <v>/contacts</v>
+        <v>/tracking</v>
       </c>
       <c r="H34" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1463,10 +1463,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F35" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G35" t="str">
-        <v>/dashboard</v>
+        <v>/verify-email</v>
       </c>
       <c r="H35" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1492,10 +1492,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F36" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G36" t="str">
-        <v>/history</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H36" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1521,10 +1521,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F37" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G37" t="str">
-        <v>/login</v>
+        <v>/volunteer</v>
       </c>
       <c r="H37" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1550,10 +1550,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F38" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G38" t="str">
-        <v>/profile</v>
+        <v>*</v>
       </c>
       <c r="H38" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1579,10 +1579,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F39" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G39" t="str">
-        <v>/register</v>
+        <v>/</v>
       </c>
       <c r="H39" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1608,10 +1608,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F40" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G40" t="str">
-        <v>/send-sos</v>
+        <v>/admin</v>
       </c>
       <c r="H40" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1637,10 +1637,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F41" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G41" t="str">
-        <v>/settings</v>
+        <v>/chat</v>
       </c>
       <c r="H41" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1666,10 +1666,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F42" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G42" t="str">
-        <v>/tracking</v>
+        <v>/contacts</v>
       </c>
       <c r="H42" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1695,10 +1695,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F43" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G43" t="str">
-        <v>/volunteer</v>
+        <v>/dashboard</v>
       </c>
       <c r="H43" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1727,7 +1727,7 @@
         <v>src/App.tsx</v>
       </c>
       <c r="G44" t="str">
-        <v>*</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H44" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1753,10 +1753,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F45" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G45" t="str">
-        <v>/</v>
+        <v>/history</v>
       </c>
       <c r="H45" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1782,10 +1782,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F46" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G46" t="str">
-        <v>/admin</v>
+        <v>/login</v>
       </c>
       <c r="H46" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1811,10 +1811,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F47" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G47" t="str">
-        <v>/chat</v>
+        <v>/profile</v>
       </c>
       <c r="H47" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1840,10 +1840,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F48" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G48" t="str">
-        <v>/contacts</v>
+        <v>/register</v>
       </c>
       <c r="H48" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1869,10 +1869,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F49" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G49" t="str">
-        <v>/dashboard</v>
+        <v>/reset-password</v>
       </c>
       <c r="H49" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1898,10 +1898,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F50" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G50" t="str">
-        <v>/history</v>
+        <v>/send-sos</v>
       </c>
       <c r="H50" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -1927,10 +1927,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F51" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G51" t="str">
-        <v>/login</v>
+        <v>/settings</v>
       </c>
       <c r="H51" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2170,10 +2170,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F8" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G8" t="str">
-        <v>/history</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H8" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2199,10 +2199,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F9" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G9" t="str">
-        <v>/login</v>
+        <v>/history</v>
       </c>
       <c r="H9" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2228,10 +2228,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F10" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G10" t="str">
-        <v>/profile</v>
+        <v>/login</v>
       </c>
       <c r="H10" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2257,10 +2257,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F11" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G11" t="str">
-        <v>/register</v>
+        <v>/profile</v>
       </c>
       <c r="H11" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2286,10 +2286,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F12" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G12" t="str">
-        <v>/send-sos</v>
+        <v>/register</v>
       </c>
       <c r="H12" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2315,10 +2315,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F13" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G13" t="str">
-        <v>/settings</v>
+        <v>/reset-password</v>
       </c>
       <c r="H13" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2344,10 +2344,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F14" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G14" t="str">
-        <v>/tracking</v>
+        <v>/send-sos</v>
       </c>
       <c r="H14" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2373,10 +2373,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F15" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G15" t="str">
-        <v>/volunteer</v>
+        <v>/settings</v>
       </c>
       <c r="H15" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2402,10 +2402,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F16" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G16" t="str">
-        <v>*</v>
+        <v>/tracking</v>
       </c>
       <c r="H16" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2431,10 +2431,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F17" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G17" t="str">
-        <v>/</v>
+        <v>/verify-email</v>
       </c>
       <c r="H17" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2460,10 +2460,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F18" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G18" t="str">
-        <v>/admin</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H18" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2489,10 +2489,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F19" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G19" t="str">
-        <v>/chat</v>
+        <v>/volunteer</v>
       </c>
       <c r="H19" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2518,10 +2518,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F20" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G20" t="str">
-        <v>/contacts</v>
+        <v>*</v>
       </c>
       <c r="H20" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2547,10 +2547,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F21" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G21" t="str">
-        <v>/dashboard</v>
+        <v>/</v>
       </c>
       <c r="H21" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2576,10 +2576,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F22" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G22" t="str">
-        <v>/history</v>
+        <v>/admin</v>
       </c>
       <c r="H22" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2605,10 +2605,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F23" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G23" t="str">
-        <v>/login</v>
+        <v>/chat</v>
       </c>
       <c r="H23" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2634,10 +2634,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F24" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G24" t="str">
-        <v>/profile</v>
+        <v>/contacts</v>
       </c>
       <c r="H24" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2663,10 +2663,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F25" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G25" t="str">
-        <v>/register</v>
+        <v>/dashboard</v>
       </c>
       <c r="H25" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2692,10 +2692,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F26" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G26" t="str">
-        <v>/send-sos</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H26" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2721,10 +2721,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F27" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G27" t="str">
-        <v>/settings</v>
+        <v>/history</v>
       </c>
       <c r="H27" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2750,10 +2750,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F28" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G28" t="str">
-        <v>/tracking</v>
+        <v>/login</v>
       </c>
       <c r="H28" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2779,10 +2779,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F29" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G29" t="str">
-        <v>/volunteer</v>
+        <v>/profile</v>
       </c>
       <c r="H29" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2808,10 +2808,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F30" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G30" t="str">
-        <v>*</v>
+        <v>/register</v>
       </c>
       <c r="H30" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2837,10 +2837,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F31" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G31" t="str">
-        <v>/</v>
+        <v>/reset-password</v>
       </c>
       <c r="H31" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2866,10 +2866,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F32" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G32" t="str">
-        <v>/admin</v>
+        <v>/send-sos</v>
       </c>
       <c r="H32" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2895,10 +2895,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F33" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G33" t="str">
-        <v>/chat</v>
+        <v>/settings</v>
       </c>
       <c r="H33" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2924,10 +2924,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F34" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G34" t="str">
-        <v>/contacts</v>
+        <v>/tracking</v>
       </c>
       <c r="H34" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2953,10 +2953,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F35" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G35" t="str">
-        <v>/dashboard</v>
+        <v>/verify-email</v>
       </c>
       <c r="H35" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -2982,10 +2982,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F36" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G36" t="str">
-        <v>/history</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H36" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3011,10 +3011,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F37" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G37" t="str">
-        <v>/login</v>
+        <v>/volunteer</v>
       </c>
       <c r="H37" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3040,10 +3040,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F38" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G38" t="str">
-        <v>/profile</v>
+        <v>*</v>
       </c>
       <c r="H38" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3069,10 +3069,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F39" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G39" t="str">
-        <v>/register</v>
+        <v>/</v>
       </c>
       <c r="H39" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3098,10 +3098,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F40" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G40" t="str">
-        <v>/send-sos</v>
+        <v>/admin</v>
       </c>
       <c r="H40" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3127,10 +3127,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F41" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G41" t="str">
-        <v>/settings</v>
+        <v>/chat</v>
       </c>
       <c r="H41" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3156,10 +3156,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F42" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G42" t="str">
-        <v>/tracking</v>
+        <v>/contacts</v>
       </c>
       <c r="H42" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3185,10 +3185,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F43" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G43" t="str">
-        <v>/volunteer</v>
+        <v>/dashboard</v>
       </c>
       <c r="H43" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3217,7 +3217,7 @@
         <v>src/App.tsx</v>
       </c>
       <c r="G44" t="str">
-        <v>*</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H44" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3243,10 +3243,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F45" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G45" t="str">
-        <v>/</v>
+        <v>/history</v>
       </c>
       <c r="H45" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3272,10 +3272,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F46" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G46" t="str">
-        <v>/admin</v>
+        <v>/login</v>
       </c>
       <c r="H46" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3301,10 +3301,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F47" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G47" t="str">
-        <v>/chat</v>
+        <v>/profile</v>
       </c>
       <c r="H47" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3330,10 +3330,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F48" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G48" t="str">
-        <v>/contacts</v>
+        <v>/register</v>
       </c>
       <c r="H48" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3359,10 +3359,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F49" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G49" t="str">
-        <v>/dashboard</v>
+        <v>/reset-password</v>
       </c>
       <c r="H49" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3388,10 +3388,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F50" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G50" t="str">
-        <v>/history</v>
+        <v>/send-sos</v>
       </c>
       <c r="H50" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3417,10 +3417,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F51" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G51" t="str">
-        <v>/login</v>
+        <v>/settings</v>
       </c>
       <c r="H51" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3446,10 +3446,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F52" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G52" t="str">
-        <v>/profile</v>
+        <v>/tracking</v>
       </c>
       <c r="H52" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3475,10 +3475,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F53" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G53" t="str">
-        <v>/register</v>
+        <v>/verify-email</v>
       </c>
       <c r="H53" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3504,10 +3504,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F54" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G54" t="str">
-        <v>/send-sos</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H54" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3533,10 +3533,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F55" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G55" t="str">
-        <v>/settings</v>
+        <v>/volunteer</v>
       </c>
       <c r="H55" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3562,10 +3562,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F56" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G56" t="str">
-        <v>/tracking</v>
+        <v>*</v>
       </c>
       <c r="H56" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3591,10 +3591,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F57" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G57" t="str">
-        <v>/volunteer</v>
+        <v>/</v>
       </c>
       <c r="H57" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3620,10 +3620,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F58" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G58" t="str">
-        <v>*</v>
+        <v>/admin</v>
       </c>
       <c r="H58" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3649,10 +3649,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F59" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G59" t="str">
-        <v>/</v>
+        <v>/chat</v>
       </c>
       <c r="H59" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3678,10 +3678,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F60" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G60" t="str">
-        <v>/admin</v>
+        <v>/contacts</v>
       </c>
       <c r="H60" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3707,10 +3707,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F61" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G61" t="str">
-        <v>/chat</v>
+        <v>/dashboard</v>
       </c>
       <c r="H61" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3736,10 +3736,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F62" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G62" t="str">
-        <v>/contacts</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H62" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3765,10 +3765,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F63" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G63" t="str">
-        <v>/dashboard</v>
+        <v>/history</v>
       </c>
       <c r="H63" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3794,10 +3794,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F64" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G64" t="str">
-        <v>/history</v>
+        <v>/login</v>
       </c>
       <c r="H64" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3823,10 +3823,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F65" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G65" t="str">
-        <v>/login</v>
+        <v>/profile</v>
       </c>
       <c r="H65" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3852,10 +3852,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F66" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G66" t="str">
-        <v>/profile</v>
+        <v>/register</v>
       </c>
       <c r="H66" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3881,10 +3881,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F67" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G67" t="str">
-        <v>/register</v>
+        <v>/reset-password</v>
       </c>
       <c r="H67" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -3997,10 +3997,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F71" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G71" t="str">
-        <v>/volunteer</v>
+        <v>/verify-email</v>
       </c>
       <c r="H71" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4029,7 +4029,7 @@
         <v>src/App.tsx</v>
       </c>
       <c r="G72" t="str">
-        <v>*</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H72" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4055,10 +4055,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F73" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G73" t="str">
-        <v>/</v>
+        <v>/volunteer</v>
       </c>
       <c r="H73" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4084,10 +4084,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F74" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G74" t="str">
-        <v>/admin</v>
+        <v>*</v>
       </c>
       <c r="H74" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4113,10 +4113,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F75" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G75" t="str">
-        <v>/chat</v>
+        <v>/</v>
       </c>
       <c r="H75" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4142,10 +4142,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F76" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G76" t="str">
-        <v>/contacts</v>
+        <v>/admin</v>
       </c>
       <c r="H76" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4171,10 +4171,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F77" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G77" t="str">
-        <v>/dashboard</v>
+        <v>/chat</v>
       </c>
       <c r="H77" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4200,10 +4200,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F78" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G78" t="str">
-        <v>/history</v>
+        <v>/contacts</v>
       </c>
       <c r="H78" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4229,10 +4229,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F79" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G79" t="str">
-        <v>/login</v>
+        <v>/dashboard</v>
       </c>
       <c r="H79" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4258,10 +4258,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F80" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G80" t="str">
-        <v>/profile</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H80" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4287,10 +4287,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F81" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G81" t="str">
-        <v>/register</v>
+        <v>/history</v>
       </c>
       <c r="H81" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4316,10 +4316,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F82" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G82" t="str">
-        <v>/send-sos</v>
+        <v>/login</v>
       </c>
       <c r="H82" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4345,10 +4345,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F83" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G83" t="str">
-        <v>/settings</v>
+        <v>/profile</v>
       </c>
       <c r="H83" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4374,10 +4374,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F84" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G84" t="str">
-        <v>/tracking</v>
+        <v>/register</v>
       </c>
       <c r="H84" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4403,10 +4403,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F85" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G85" t="str">
-        <v>/volunteer</v>
+        <v>/reset-password</v>
       </c>
       <c r="H85" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4432,10 +4432,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F86" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G86" t="str">
-        <v>*</v>
+        <v>/send-sos</v>
       </c>
       <c r="H86" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4461,10 +4461,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F87" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G87" t="str">
-        <v>/</v>
+        <v>/settings</v>
       </c>
       <c r="H87" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4490,10 +4490,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F88" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G88" t="str">
-        <v>/admin</v>
+        <v>/tracking</v>
       </c>
       <c r="H88" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4519,10 +4519,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F89" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G89" t="str">
-        <v>/chat</v>
+        <v>/verify-email</v>
       </c>
       <c r="H89" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4548,10 +4548,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F90" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G90" t="str">
-        <v>/contacts</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H90" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4577,10 +4577,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F91" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G91" t="str">
-        <v>/dashboard</v>
+        <v>/volunteer</v>
       </c>
       <c r="H91" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4606,10 +4606,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F92" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G92" t="str">
-        <v>/history</v>
+        <v>*</v>
       </c>
       <c r="H92" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4635,10 +4635,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F93" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G93" t="str">
-        <v>/login</v>
+        <v>/</v>
       </c>
       <c r="H93" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4664,10 +4664,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F94" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G94" t="str">
-        <v>/profile</v>
+        <v>/admin</v>
       </c>
       <c r="H94" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4693,10 +4693,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F95" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G95" t="str">
-        <v>/register</v>
+        <v>/chat</v>
       </c>
       <c r="H95" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4722,10 +4722,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F96" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G96" t="str">
-        <v>/send-sos</v>
+        <v>/contacts</v>
       </c>
       <c r="H96" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4751,10 +4751,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F97" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G97" t="str">
-        <v>/settings</v>
+        <v>/dashboard</v>
       </c>
       <c r="H97" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4780,10 +4780,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F98" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G98" t="str">
-        <v>/tracking</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H98" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4809,10 +4809,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F99" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G99" t="str">
-        <v>/volunteer</v>
+        <v>/history</v>
       </c>
       <c r="H99" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4838,10 +4838,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F100" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G100" t="str">
-        <v>*</v>
+        <v>/login</v>
       </c>
       <c r="H100" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4867,10 +4867,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F101" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G101" t="str">
-        <v>/</v>
+        <v>/profile</v>
       </c>
       <c r="H101" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4896,10 +4896,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F102" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G102" t="str">
-        <v>/admin</v>
+        <v>/register</v>
       </c>
       <c r="H102" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4925,10 +4925,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F103" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G103" t="str">
-        <v>/chat</v>
+        <v>/reset-password</v>
       </c>
       <c r="H103" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4954,10 +4954,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F104" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G104" t="str">
-        <v>/contacts</v>
+        <v>/send-sos</v>
       </c>
       <c r="H104" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -4983,10 +4983,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F105" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G105" t="str">
-        <v>/dashboard</v>
+        <v>/settings</v>
       </c>
       <c r="H105" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5012,10 +5012,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F106" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G106" t="str">
-        <v>/history</v>
+        <v>/tracking</v>
       </c>
       <c r="H106" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5041,10 +5041,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F107" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G107" t="str">
-        <v>/login</v>
+        <v>/verify-email</v>
       </c>
       <c r="H107" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5070,10 +5070,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F108" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G108" t="str">
-        <v>/profile</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H108" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5099,10 +5099,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F109" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G109" t="str">
-        <v>/register</v>
+        <v>/volunteer</v>
       </c>
       <c r="H109" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5128,10 +5128,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F110" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G110" t="str">
-        <v>/send-sos</v>
+        <v>*</v>
       </c>
       <c r="H110" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5157,10 +5157,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F111" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G111" t="str">
-        <v>/settings</v>
+        <v>/</v>
       </c>
       <c r="H111" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5186,10 +5186,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F112" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G112" t="str">
-        <v>/tracking</v>
+        <v>/admin</v>
       </c>
       <c r="H112" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5215,10 +5215,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F113" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G113" t="str">
-        <v>/volunteer</v>
+        <v>/chat</v>
       </c>
       <c r="H113" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5244,10 +5244,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F114" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G114" t="str">
-        <v>*</v>
+        <v>/contacts</v>
       </c>
       <c r="H114" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5273,10 +5273,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F115" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G115" t="str">
-        <v>/</v>
+        <v>/dashboard</v>
       </c>
       <c r="H115" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5302,10 +5302,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F116" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G116" t="str">
-        <v>/admin</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H116" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5331,10 +5331,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F117" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G117" t="str">
-        <v>/chat</v>
+        <v>/history</v>
       </c>
       <c r="H117" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5360,10 +5360,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F118" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G118" t="str">
-        <v>/contacts</v>
+        <v>/login</v>
       </c>
       <c r="H118" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5389,10 +5389,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F119" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G119" t="str">
-        <v>/dashboard</v>
+        <v>/profile</v>
       </c>
       <c r="H119" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5418,10 +5418,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F120" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G120" t="str">
-        <v>/history</v>
+        <v>/register</v>
       </c>
       <c r="H120" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5447,10 +5447,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F121" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G121" t="str">
-        <v>/login</v>
+        <v>/reset-password</v>
       </c>
       <c r="H121" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5476,10 +5476,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F122" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G122" t="str">
-        <v>/profile</v>
+        <v>/send-sos</v>
       </c>
       <c r="H122" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5505,10 +5505,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F123" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G123" t="str">
-        <v>/register</v>
+        <v>/settings</v>
       </c>
       <c r="H123" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5534,10 +5534,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F124" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G124" t="str">
-        <v>/send-sos</v>
+        <v>/tracking</v>
       </c>
       <c r="H124" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5563,10 +5563,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F125" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G125" t="str">
-        <v>/settings</v>
+        <v>/verify-email</v>
       </c>
       <c r="H125" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5592,10 +5592,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F126" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G126" t="str">
-        <v>/tracking</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H126" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5824,10 +5824,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F134" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G134" t="str">
-        <v>/history</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H134" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5853,10 +5853,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F135" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G135" t="str">
-        <v>/login</v>
+        <v>/history</v>
       </c>
       <c r="H135" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5882,10 +5882,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F136" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G136" t="str">
-        <v>/profile</v>
+        <v>/login</v>
       </c>
       <c r="H136" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5911,10 +5911,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F137" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G137" t="str">
-        <v>/register</v>
+        <v>/profile</v>
       </c>
       <c r="H137" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5940,10 +5940,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F138" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G138" t="str">
-        <v>/send-sos</v>
+        <v>/register</v>
       </c>
       <c r="H138" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5969,10 +5969,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F139" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G139" t="str">
-        <v>/settings</v>
+        <v>/reset-password</v>
       </c>
       <c r="H139" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -5998,10 +5998,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F140" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G140" t="str">
-        <v>/tracking</v>
+        <v>/send-sos</v>
       </c>
       <c r="H140" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6027,10 +6027,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F141" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G141" t="str">
-        <v>/volunteer</v>
+        <v>/settings</v>
       </c>
       <c r="H141" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6056,10 +6056,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F142" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G142" t="str">
-        <v>*</v>
+        <v>/tracking</v>
       </c>
       <c r="H142" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6085,10 +6085,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F143" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G143" t="str">
-        <v>/</v>
+        <v>/verify-email</v>
       </c>
       <c r="H143" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6114,10 +6114,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F144" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G144" t="str">
-        <v>/admin</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H144" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6143,10 +6143,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F145" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G145" t="str">
-        <v>/chat</v>
+        <v>/volunteer</v>
       </c>
       <c r="H145" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6172,10 +6172,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F146" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G146" t="str">
-        <v>/contacts</v>
+        <v>*</v>
       </c>
       <c r="H146" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6201,10 +6201,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F147" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G147" t="str">
-        <v>/dashboard</v>
+        <v>/</v>
       </c>
       <c r="H147" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6230,10 +6230,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F148" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G148" t="str">
-        <v>/history</v>
+        <v>/admin</v>
       </c>
       <c r="H148" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6259,10 +6259,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F149" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G149" t="str">
-        <v>/login</v>
+        <v>/chat</v>
       </c>
       <c r="H149" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6288,10 +6288,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F150" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G150" t="str">
-        <v>/profile</v>
+        <v>/contacts</v>
       </c>
       <c r="H150" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6317,10 +6317,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F151" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G151" t="str">
-        <v>/register</v>
+        <v>/dashboard</v>
       </c>
       <c r="H151" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6346,10 +6346,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F152" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G152" t="str">
-        <v>/send-sos</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H152" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6375,10 +6375,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F153" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G153" t="str">
-        <v>/settings</v>
+        <v>/history</v>
       </c>
       <c r="H153" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6404,10 +6404,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F154" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G154" t="str">
-        <v>/tracking</v>
+        <v>/login</v>
       </c>
       <c r="H154" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6433,10 +6433,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F155" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G155" t="str">
-        <v>/volunteer</v>
+        <v>/profile</v>
       </c>
       <c r="H155" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6462,10 +6462,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F156" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G156" t="str">
-        <v>*</v>
+        <v>/register</v>
       </c>
       <c r="H156" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6491,10 +6491,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F157" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G157" t="str">
-        <v>/</v>
+        <v>/reset-password</v>
       </c>
       <c r="H157" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6520,10 +6520,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F158" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G158" t="str">
-        <v>/admin</v>
+        <v>/send-sos</v>
       </c>
       <c r="H158" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6549,10 +6549,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F159" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G159" t="str">
-        <v>/chat</v>
+        <v>/settings</v>
       </c>
       <c r="H159" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6578,10 +6578,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F160" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G160" t="str">
-        <v>/contacts</v>
+        <v>/tracking</v>
       </c>
       <c r="H160" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6607,10 +6607,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F161" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G161" t="str">
-        <v>/dashboard</v>
+        <v>/verify-email</v>
       </c>
       <c r="H161" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6636,10 +6636,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F162" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G162" t="str">
-        <v>/history</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H162" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6665,10 +6665,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F163" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G163" t="str">
-        <v>/login</v>
+        <v>/volunteer</v>
       </c>
       <c r="H163" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6694,10 +6694,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F164" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G164" t="str">
-        <v>/profile</v>
+        <v>*</v>
       </c>
       <c r="H164" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6723,10 +6723,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F165" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G165" t="str">
-        <v>/register</v>
+        <v>/</v>
       </c>
       <c r="H165" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6752,10 +6752,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F166" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G166" t="str">
-        <v>/send-sos</v>
+        <v>/admin</v>
       </c>
       <c r="H166" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6781,10 +6781,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F167" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G167" t="str">
-        <v>/settings</v>
+        <v>/chat</v>
       </c>
       <c r="H167" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6810,10 +6810,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F168" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G168" t="str">
-        <v>/tracking</v>
+        <v>/contacts</v>
       </c>
       <c r="H168" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6839,10 +6839,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F169" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G169" t="str">
-        <v>/volunteer</v>
+        <v>/dashboard</v>
       </c>
       <c r="H169" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6871,7 +6871,7 @@
         <v>src/App.tsx</v>
       </c>
       <c r="G170" t="str">
-        <v>*</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H170" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6897,10 +6897,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F171" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G171" t="str">
-        <v>/</v>
+        <v>/history</v>
       </c>
       <c r="H171" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6926,10 +6926,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F172" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G172" t="str">
-        <v>/admin</v>
+        <v>/login</v>
       </c>
       <c r="H172" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6955,10 +6955,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F173" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G173" t="str">
-        <v>/chat</v>
+        <v>/profile</v>
       </c>
       <c r="H173" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -6984,10 +6984,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F174" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G174" t="str">
-        <v>/contacts</v>
+        <v>/register</v>
       </c>
       <c r="H174" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7013,10 +7013,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F175" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G175" t="str">
-        <v>/dashboard</v>
+        <v>/reset-password</v>
       </c>
       <c r="H175" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7042,10 +7042,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F176" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G176" t="str">
-        <v>/history</v>
+        <v>/send-sos</v>
       </c>
       <c r="H176" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7071,10 +7071,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F177" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G177" t="str">
-        <v>/login</v>
+        <v>/settings</v>
       </c>
       <c r="H177" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7100,10 +7100,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F178" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G178" t="str">
-        <v>/profile</v>
+        <v>/tracking</v>
       </c>
       <c r="H178" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7129,10 +7129,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F179" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G179" t="str">
-        <v>/register</v>
+        <v>/verify-email</v>
       </c>
       <c r="H179" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7158,10 +7158,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F180" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G180" t="str">
-        <v>/send-sos</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H180" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7187,10 +7187,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F181" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G181" t="str">
-        <v>/settings</v>
+        <v>/volunteer</v>
       </c>
       <c r="H181" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7216,10 +7216,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F182" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G182" t="str">
-        <v>/tracking</v>
+        <v>*</v>
       </c>
       <c r="H182" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7245,10 +7245,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F183" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G183" t="str">
-        <v>/volunteer</v>
+        <v>/</v>
       </c>
       <c r="H183" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7274,10 +7274,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F184" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G184" t="str">
-        <v>*</v>
+        <v>/admin</v>
       </c>
       <c r="H184" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7303,10 +7303,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F185" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G185" t="str">
-        <v>/</v>
+        <v>/chat</v>
       </c>
       <c r="H185" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7332,10 +7332,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F186" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G186" t="str">
-        <v>/admin</v>
+        <v>/contacts</v>
       </c>
       <c r="H186" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7361,10 +7361,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F187" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G187" t="str">
-        <v>/chat</v>
+        <v>/dashboard</v>
       </c>
       <c r="H187" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7390,10 +7390,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F188" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G188" t="str">
-        <v>/contacts</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H188" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7419,10 +7419,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F189" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G189" t="str">
-        <v>/dashboard</v>
+        <v>/history</v>
       </c>
       <c r="H189" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7448,10 +7448,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F190" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G190" t="str">
-        <v>/history</v>
+        <v>/login</v>
       </c>
       <c r="H190" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7477,10 +7477,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F191" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G191" t="str">
-        <v>/login</v>
+        <v>/profile</v>
       </c>
       <c r="H191" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7506,10 +7506,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F192" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G192" t="str">
-        <v>/profile</v>
+        <v>/register</v>
       </c>
       <c r="H192" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7535,10 +7535,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F193" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G193" t="str">
-        <v>/register</v>
+        <v>/reset-password</v>
       </c>
       <c r="H193" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7651,10 +7651,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F197" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G197" t="str">
-        <v>/volunteer</v>
+        <v>/verify-email</v>
       </c>
       <c r="H197" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7683,7 +7683,7 @@
         <v>src/App.tsx</v>
       </c>
       <c r="G198" t="str">
-        <v>*</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H198" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7709,10 +7709,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F199" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G199" t="str">
-        <v>/</v>
+        <v>/volunteer</v>
       </c>
       <c r="H199" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7738,10 +7738,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F200" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G200" t="str">
-        <v>/admin</v>
+        <v>*</v>
       </c>
       <c r="H200" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7767,10 +7767,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F201" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G201" t="str">
-        <v>/chat</v>
+        <v>/</v>
       </c>
       <c r="H201" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7796,10 +7796,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F202" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G202" t="str">
-        <v>/contacts</v>
+        <v>/admin</v>
       </c>
       <c r="H202" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7825,10 +7825,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F203" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G203" t="str">
-        <v>/dashboard</v>
+        <v>/chat</v>
       </c>
       <c r="H203" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7854,10 +7854,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F204" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G204" t="str">
-        <v>/history</v>
+        <v>/contacts</v>
       </c>
       <c r="H204" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7883,10 +7883,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F205" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G205" t="str">
-        <v>/login</v>
+        <v>/dashboard</v>
       </c>
       <c r="H205" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7912,10 +7912,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F206" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G206" t="str">
-        <v>/profile</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H206" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7941,10 +7941,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F207" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G207" t="str">
-        <v>/register</v>
+        <v>/history</v>
       </c>
       <c r="H207" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7970,10 +7970,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F208" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G208" t="str">
-        <v>/send-sos</v>
+        <v>/login</v>
       </c>
       <c r="H208" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -7999,10 +7999,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F209" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G209" t="str">
-        <v>/settings</v>
+        <v>/profile</v>
       </c>
       <c r="H209" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8028,10 +8028,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F210" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G210" t="str">
-        <v>/tracking</v>
+        <v>/register</v>
       </c>
       <c r="H210" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8057,10 +8057,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F211" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G211" t="str">
-        <v>/volunteer</v>
+        <v>/reset-password</v>
       </c>
       <c r="H211" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8086,10 +8086,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F212" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G212" t="str">
-        <v>*</v>
+        <v>/send-sos</v>
       </c>
       <c r="H212" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8115,10 +8115,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F213" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G213" t="str">
-        <v>/</v>
+        <v>/settings</v>
       </c>
       <c r="H213" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8144,10 +8144,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F214" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G214" t="str">
-        <v>/admin</v>
+        <v>/tracking</v>
       </c>
       <c r="H214" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8173,10 +8173,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F215" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G215" t="str">
-        <v>/chat</v>
+        <v>/verify-email</v>
       </c>
       <c r="H215" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8202,10 +8202,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F216" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G216" t="str">
-        <v>/contacts</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H216" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8231,10 +8231,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F217" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G217" t="str">
-        <v>/dashboard</v>
+        <v>/volunteer</v>
       </c>
       <c r="H217" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8260,10 +8260,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F218" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G218" t="str">
-        <v>/history</v>
+        <v>*</v>
       </c>
       <c r="H218" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8289,10 +8289,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F219" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G219" t="str">
-        <v>/login</v>
+        <v>/</v>
       </c>
       <c r="H219" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8318,10 +8318,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F220" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G220" t="str">
-        <v>/profile</v>
+        <v>/admin</v>
       </c>
       <c r="H220" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8347,10 +8347,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F221" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G221" t="str">
-        <v>/register</v>
+        <v>/chat</v>
       </c>
       <c r="H221" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8376,10 +8376,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F222" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G222" t="str">
-        <v>/send-sos</v>
+        <v>/contacts</v>
       </c>
       <c r="H222" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8405,10 +8405,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F223" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G223" t="str">
-        <v>/settings</v>
+        <v>/dashboard</v>
       </c>
       <c r="H223" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8434,10 +8434,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F224" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G224" t="str">
-        <v>/tracking</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H224" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8463,10 +8463,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F225" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G225" t="str">
-        <v>/volunteer</v>
+        <v>/history</v>
       </c>
       <c r="H225" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8492,10 +8492,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F226" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G226" t="str">
-        <v>*</v>
+        <v>/login</v>
       </c>
       <c r="H226" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8521,10 +8521,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F227" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G227" t="str">
-        <v>/</v>
+        <v>/profile</v>
       </c>
       <c r="H227" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8550,10 +8550,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F228" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G228" t="str">
-        <v>/admin</v>
+        <v>/register</v>
       </c>
       <c r="H228" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8579,10 +8579,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F229" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G229" t="str">
-        <v>/chat</v>
+        <v>/reset-password</v>
       </c>
       <c r="H229" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8608,10 +8608,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F230" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G230" t="str">
-        <v>/contacts</v>
+        <v>/send-sos</v>
       </c>
       <c r="H230" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8637,10 +8637,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F231" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G231" t="str">
-        <v>/dashboard</v>
+        <v>/settings</v>
       </c>
       <c r="H231" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8666,10 +8666,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F232" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G232" t="str">
-        <v>/history</v>
+        <v>/tracking</v>
       </c>
       <c r="H232" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8695,10 +8695,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F233" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G233" t="str">
-        <v>/login</v>
+        <v>/verify-email</v>
       </c>
       <c r="H233" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8724,10 +8724,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F234" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G234" t="str">
-        <v>/profile</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H234" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8753,10 +8753,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F235" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G235" t="str">
-        <v>/register</v>
+        <v>/volunteer</v>
       </c>
       <c r="H235" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8782,10 +8782,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F236" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G236" t="str">
-        <v>/send-sos</v>
+        <v>*</v>
       </c>
       <c r="H236" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8811,10 +8811,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F237" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G237" t="str">
-        <v>/settings</v>
+        <v>/</v>
       </c>
       <c r="H237" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8840,10 +8840,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F238" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G238" t="str">
-        <v>/tracking</v>
+        <v>/admin</v>
       </c>
       <c r="H238" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8869,10 +8869,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F239" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G239" t="str">
-        <v>/volunteer</v>
+        <v>/chat</v>
       </c>
       <c r="H239" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8898,10 +8898,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F240" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G240" t="str">
-        <v>*</v>
+        <v>/contacts</v>
       </c>
       <c r="H240" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8927,10 +8927,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F241" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G241" t="str">
-        <v>/</v>
+        <v>/dashboard</v>
       </c>
       <c r="H241" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8956,10 +8956,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F242" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G242" t="str">
-        <v>/admin</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H242" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -8985,10 +8985,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F243" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G243" t="str">
-        <v>/chat</v>
+        <v>/history</v>
       </c>
       <c r="H243" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9014,10 +9014,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F244" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G244" t="str">
-        <v>/contacts</v>
+        <v>/login</v>
       </c>
       <c r="H244" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9043,10 +9043,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F245" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G245" t="str">
-        <v>/dashboard</v>
+        <v>/profile</v>
       </c>
       <c r="H245" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9072,10 +9072,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F246" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G246" t="str">
-        <v>/history</v>
+        <v>/register</v>
       </c>
       <c r="H246" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9101,10 +9101,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F247" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G247" t="str">
-        <v>/login</v>
+        <v>/reset-password</v>
       </c>
       <c r="H247" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9130,10 +9130,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F248" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G248" t="str">
-        <v>/profile</v>
+        <v>/send-sos</v>
       </c>
       <c r="H248" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9159,10 +9159,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F249" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G249" t="str">
-        <v>/register</v>
+        <v>/settings</v>
       </c>
       <c r="H249" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9188,10 +9188,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F250" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G250" t="str">
-        <v>/send-sos</v>
+        <v>/tracking</v>
       </c>
       <c r="H250" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9217,10 +9217,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F251" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G251" t="str">
-        <v>/settings</v>
+        <v>/verify-email</v>
       </c>
       <c r="H251" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9246,10 +9246,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F252" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G252" t="str">
-        <v>/tracking</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H252" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9478,10 +9478,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F260" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G260" t="str">
-        <v>/history</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H260" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9507,10 +9507,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F261" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G261" t="str">
-        <v>/login</v>
+        <v>/history</v>
       </c>
       <c r="H261" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9536,10 +9536,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F262" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G262" t="str">
-        <v>/profile</v>
+        <v>/login</v>
       </c>
       <c r="H262" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9565,10 +9565,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F263" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G263" t="str">
-        <v>/register</v>
+        <v>/profile</v>
       </c>
       <c r="H263" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9594,10 +9594,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F264" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G264" t="str">
-        <v>/send-sos</v>
+        <v>/register</v>
       </c>
       <c r="H264" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9623,10 +9623,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F265" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G265" t="str">
-        <v>/settings</v>
+        <v>/reset-password</v>
       </c>
       <c r="H265" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9652,10 +9652,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F266" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G266" t="str">
-        <v>/tracking</v>
+        <v>/send-sos</v>
       </c>
       <c r="H266" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9681,10 +9681,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F267" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G267" t="str">
-        <v>/volunteer</v>
+        <v>/settings</v>
       </c>
       <c r="H267" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9710,10 +9710,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F268" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G268" t="str">
-        <v>*</v>
+        <v>/tracking</v>
       </c>
       <c r="H268" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9739,10 +9739,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F269" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G269" t="str">
-        <v>/</v>
+        <v>/verify-email</v>
       </c>
       <c r="H269" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9768,10 +9768,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F270" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G270" t="str">
-        <v>/admin</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H270" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9797,10 +9797,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F271" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G271" t="str">
-        <v>/chat</v>
+        <v>/volunteer</v>
       </c>
       <c r="H271" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9826,10 +9826,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F272" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G272" t="str">
-        <v>/contacts</v>
+        <v>*</v>
       </c>
       <c r="H272" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9855,10 +9855,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F273" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G273" t="str">
-        <v>/dashboard</v>
+        <v>/</v>
       </c>
       <c r="H273" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9884,10 +9884,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F274" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G274" t="str">
-        <v>/history</v>
+        <v>/admin</v>
       </c>
       <c r="H274" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9913,10 +9913,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F275" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G275" t="str">
-        <v>/login</v>
+        <v>/chat</v>
       </c>
       <c r="H275" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9942,10 +9942,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F276" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G276" t="str">
-        <v>/profile</v>
+        <v>/contacts</v>
       </c>
       <c r="H276" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -9971,10 +9971,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F277" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G277" t="str">
-        <v>/register</v>
+        <v>/dashboard</v>
       </c>
       <c r="H277" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10000,10 +10000,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F278" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G278" t="str">
-        <v>/send-sos</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H278" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10029,10 +10029,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F279" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G279" t="str">
-        <v>/settings</v>
+        <v>/history</v>
       </c>
       <c r="H279" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10058,10 +10058,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F280" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G280" t="str">
-        <v>/tracking</v>
+        <v>/login</v>
       </c>
       <c r="H280" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10087,10 +10087,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F281" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G281" t="str">
-        <v>/volunteer</v>
+        <v>/profile</v>
       </c>
       <c r="H281" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10116,10 +10116,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F282" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G282" t="str">
-        <v>*</v>
+        <v>/register</v>
       </c>
       <c r="H282" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10145,10 +10145,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F283" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G283" t="str">
-        <v>/</v>
+        <v>/reset-password</v>
       </c>
       <c r="H283" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10174,10 +10174,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F284" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G284" t="str">
-        <v>/admin</v>
+        <v>/send-sos</v>
       </c>
       <c r="H284" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10203,10 +10203,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F285" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G285" t="str">
-        <v>/chat</v>
+        <v>/settings</v>
       </c>
       <c r="H285" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10232,10 +10232,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F286" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G286" t="str">
-        <v>/contacts</v>
+        <v>/tracking</v>
       </c>
       <c r="H286" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10261,10 +10261,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F287" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G287" t="str">
-        <v>/dashboard</v>
+        <v>/verify-email</v>
       </c>
       <c r="H287" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10290,10 +10290,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F288" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G288" t="str">
-        <v>/history</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H288" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10319,10 +10319,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F289" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G289" t="str">
-        <v>/login</v>
+        <v>/volunteer</v>
       </c>
       <c r="H289" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10348,10 +10348,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F290" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G290" t="str">
-        <v>/profile</v>
+        <v>*</v>
       </c>
       <c r="H290" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10377,10 +10377,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F291" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G291" t="str">
-        <v>/register</v>
+        <v>/</v>
       </c>
       <c r="H291" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10406,10 +10406,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F292" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G292" t="str">
-        <v>/send-sos</v>
+        <v>/admin</v>
       </c>
       <c r="H292" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10435,10 +10435,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F293" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G293" t="str">
-        <v>/settings</v>
+        <v>/chat</v>
       </c>
       <c r="H293" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10464,10 +10464,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F294" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G294" t="str">
-        <v>/tracking</v>
+        <v>/contacts</v>
       </c>
       <c r="H294" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10493,10 +10493,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F295" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G295" t="str">
-        <v>/volunteer</v>
+        <v>/dashboard</v>
       </c>
       <c r="H295" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10525,7 +10525,7 @@
         <v>src/App.tsx</v>
       </c>
       <c r="G296" t="str">
-        <v>*</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H296" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10551,10 +10551,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F297" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G297" t="str">
-        <v>/</v>
+        <v>/history</v>
       </c>
       <c r="H297" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10580,10 +10580,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F298" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G298" t="str">
-        <v>/admin</v>
+        <v>/login</v>
       </c>
       <c r="H298" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10609,10 +10609,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F299" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G299" t="str">
-        <v>/chat</v>
+        <v>/profile</v>
       </c>
       <c r="H299" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10638,10 +10638,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F300" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G300" t="str">
-        <v>/contacts</v>
+        <v>/register</v>
       </c>
       <c r="H300" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10667,10 +10667,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F301" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G301" t="str">
-        <v>/dashboard</v>
+        <v>/reset-password</v>
       </c>
       <c r="H301" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10696,10 +10696,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F302" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G302" t="str">
-        <v>/history</v>
+        <v>/send-sos</v>
       </c>
       <c r="H302" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10725,10 +10725,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F303" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G303" t="str">
-        <v>/login</v>
+        <v>/settings</v>
       </c>
       <c r="H303" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10754,10 +10754,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F304" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G304" t="str">
-        <v>/profile</v>
+        <v>/tracking</v>
       </c>
       <c r="H304" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10783,10 +10783,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F305" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G305" t="str">
-        <v>/register</v>
+        <v>/verify-email</v>
       </c>
       <c r="H305" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10812,10 +10812,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F306" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G306" t="str">
-        <v>/send-sos</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H306" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10841,10 +10841,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F307" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G307" t="str">
-        <v>/settings</v>
+        <v>/volunteer</v>
       </c>
       <c r="H307" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10870,10 +10870,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F308" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G308" t="str">
-        <v>/tracking</v>
+        <v>*</v>
       </c>
       <c r="H308" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10899,10 +10899,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F309" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G309" t="str">
-        <v>/volunteer</v>
+        <v>/</v>
       </c>
       <c r="H309" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10928,10 +10928,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F310" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G310" t="str">
-        <v>*</v>
+        <v>/admin</v>
       </c>
       <c r="H310" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10957,10 +10957,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F311" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G311" t="str">
-        <v>/</v>
+        <v>/chat</v>
       </c>
       <c r="H311" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -10986,10 +10986,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F312" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G312" t="str">
-        <v>/admin</v>
+        <v>/contacts</v>
       </c>
       <c r="H312" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11015,10 +11015,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F313" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G313" t="str">
-        <v>/chat</v>
+        <v>/dashboard</v>
       </c>
       <c r="H313" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11044,10 +11044,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F314" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G314" t="str">
-        <v>/contacts</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H314" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11073,10 +11073,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F315" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G315" t="str">
-        <v>/dashboard</v>
+        <v>/history</v>
       </c>
       <c r="H315" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11102,10 +11102,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F316" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G316" t="str">
-        <v>/history</v>
+        <v>/login</v>
       </c>
       <c r="H316" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11131,10 +11131,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F317" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G317" t="str">
-        <v>/login</v>
+        <v>/profile</v>
       </c>
       <c r="H317" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11160,10 +11160,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F318" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G318" t="str">
-        <v>/profile</v>
+        <v>/register</v>
       </c>
       <c r="H318" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11189,10 +11189,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F319" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G319" t="str">
-        <v>/register</v>
+        <v>/reset-password</v>
       </c>
       <c r="H319" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11305,10 +11305,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F323" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G323" t="str">
-        <v>/volunteer</v>
+        <v>/verify-email</v>
       </c>
       <c r="H323" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11337,7 +11337,7 @@
         <v>src/App.tsx</v>
       </c>
       <c r="G324" t="str">
-        <v>*</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H324" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11363,10 +11363,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F325" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G325" t="str">
-        <v>/</v>
+        <v>/volunteer</v>
       </c>
       <c r="H325" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11392,10 +11392,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F326" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G326" t="str">
-        <v>/admin</v>
+        <v>*</v>
       </c>
       <c r="H326" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11421,10 +11421,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F327" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G327" t="str">
-        <v>/chat</v>
+        <v>/</v>
       </c>
       <c r="H327" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11450,10 +11450,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F328" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G328" t="str">
-        <v>/contacts</v>
+        <v>/admin</v>
       </c>
       <c r="H328" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11479,10 +11479,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F329" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G329" t="str">
-        <v>/dashboard</v>
+        <v>/chat</v>
       </c>
       <c r="H329" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11508,10 +11508,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F330" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G330" t="str">
-        <v>/history</v>
+        <v>/contacts</v>
       </c>
       <c r="H330" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11537,10 +11537,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F331" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G331" t="str">
-        <v>/login</v>
+        <v>/dashboard</v>
       </c>
       <c r="H331" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11566,10 +11566,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F332" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G332" t="str">
-        <v>/profile</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H332" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11595,10 +11595,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F333" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G333" t="str">
-        <v>/register</v>
+        <v>/history</v>
       </c>
       <c r="H333" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11624,10 +11624,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F334" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G334" t="str">
-        <v>/send-sos</v>
+        <v>/login</v>
       </c>
       <c r="H334" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11653,10 +11653,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F335" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G335" t="str">
-        <v>/settings</v>
+        <v>/profile</v>
       </c>
       <c r="H335" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11682,10 +11682,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F336" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G336" t="str">
-        <v>/tracking</v>
+        <v>/register</v>
       </c>
       <c r="H336" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11711,10 +11711,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F337" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G337" t="str">
-        <v>/volunteer</v>
+        <v>/reset-password</v>
       </c>
       <c r="H337" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11740,10 +11740,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F338" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G338" t="str">
-        <v>*</v>
+        <v>/send-sos</v>
       </c>
       <c r="H338" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11769,10 +11769,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F339" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G339" t="str">
-        <v>/</v>
+        <v>/settings</v>
       </c>
       <c r="H339" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11798,10 +11798,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F340" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G340" t="str">
-        <v>/admin</v>
+        <v>/tracking</v>
       </c>
       <c r="H340" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11827,10 +11827,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F341" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G341" t="str">
-        <v>/chat</v>
+        <v>/verify-email</v>
       </c>
       <c r="H341" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11856,10 +11856,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F342" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G342" t="str">
-        <v>/contacts</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H342" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11885,10 +11885,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F343" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G343" t="str">
-        <v>/dashboard</v>
+        <v>/volunteer</v>
       </c>
       <c r="H343" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11914,10 +11914,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F344" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G344" t="str">
-        <v>/history</v>
+        <v>*</v>
       </c>
       <c r="H344" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11943,10 +11943,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F345" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G345" t="str">
-        <v>/login</v>
+        <v>/</v>
       </c>
       <c r="H345" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -11972,10 +11972,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F346" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G346" t="str">
-        <v>/profile</v>
+        <v>/admin</v>
       </c>
       <c r="H346" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12001,10 +12001,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F347" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G347" t="str">
-        <v>/register</v>
+        <v>/chat</v>
       </c>
       <c r="H347" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12030,10 +12030,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F348" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G348" t="str">
-        <v>/send-sos</v>
+        <v>/contacts</v>
       </c>
       <c r="H348" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12059,10 +12059,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F349" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G349" t="str">
-        <v>/settings</v>
+        <v>/dashboard</v>
       </c>
       <c r="H349" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12088,10 +12088,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F350" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G350" t="str">
-        <v>/tracking</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H350" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12117,10 +12117,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F351" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G351" t="str">
-        <v>/volunteer</v>
+        <v>/history</v>
       </c>
       <c r="H351" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12146,10 +12146,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F352" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G352" t="str">
-        <v>*</v>
+        <v>/login</v>
       </c>
       <c r="H352" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12175,10 +12175,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F353" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G353" t="str">
-        <v>/</v>
+        <v>/profile</v>
       </c>
       <c r="H353" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12204,10 +12204,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F354" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G354" t="str">
-        <v>/admin</v>
+        <v>/register</v>
       </c>
       <c r="H354" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12233,10 +12233,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F355" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G355" t="str">
-        <v>/chat</v>
+        <v>/reset-password</v>
       </c>
       <c r="H355" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12262,10 +12262,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F356" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G356" t="str">
-        <v>/contacts</v>
+        <v>/send-sos</v>
       </c>
       <c r="H356" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12291,10 +12291,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F357" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G357" t="str">
-        <v>/dashboard</v>
+        <v>/settings</v>
       </c>
       <c r="H357" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12320,10 +12320,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F358" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G358" t="str">
-        <v>/history</v>
+        <v>/tracking</v>
       </c>
       <c r="H358" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12349,10 +12349,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F359" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G359" t="str">
-        <v>/login</v>
+        <v>/verify-email</v>
       </c>
       <c r="H359" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12378,10 +12378,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F360" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G360" t="str">
-        <v>/profile</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H360" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12407,10 +12407,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F361" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G361" t="str">
-        <v>/register</v>
+        <v>/volunteer</v>
       </c>
       <c r="H361" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12436,10 +12436,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F362" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G362" t="str">
-        <v>/send-sos</v>
+        <v>*</v>
       </c>
       <c r="H362" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12465,10 +12465,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F363" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G363" t="str">
-        <v>/settings</v>
+        <v>/</v>
       </c>
       <c r="H363" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12494,10 +12494,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F364" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G364" t="str">
-        <v>/tracking</v>
+        <v>/admin</v>
       </c>
       <c r="H364" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12523,10 +12523,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F365" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G365" t="str">
-        <v>/volunteer</v>
+        <v>/chat</v>
       </c>
       <c r="H365" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12552,10 +12552,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F366" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/EmergencyContacts.tsx</v>
       </c>
       <c r="G366" t="str">
-        <v>*</v>
+        <v>/contacts</v>
       </c>
       <c r="H366" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12581,10 +12581,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F367" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/pages/Dashboard.tsx</v>
       </c>
       <c r="G367" t="str">
-        <v>/</v>
+        <v>/dashboard</v>
       </c>
       <c r="H367" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12610,10 +12610,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F368" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G368" t="str">
-        <v>/admin</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H368" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12639,10 +12639,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F369" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G369" t="str">
-        <v>/chat</v>
+        <v>/history</v>
       </c>
       <c r="H369" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12668,10 +12668,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F370" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G370" t="str">
-        <v>/contacts</v>
+        <v>/login</v>
       </c>
       <c r="H370" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12697,10 +12697,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F371" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G371" t="str">
-        <v>/dashboard</v>
+        <v>/profile</v>
       </c>
       <c r="H371" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12726,10 +12726,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F372" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G372" t="str">
-        <v>/history</v>
+        <v>/register</v>
       </c>
       <c r="H372" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12755,10 +12755,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F373" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G373" t="str">
-        <v>/login</v>
+        <v>/reset-password</v>
       </c>
       <c r="H373" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12784,10 +12784,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F374" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G374" t="str">
-        <v>/profile</v>
+        <v>/send-sos</v>
       </c>
       <c r="H374" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12813,10 +12813,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F375" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G375" t="str">
-        <v>/register</v>
+        <v>/settings</v>
       </c>
       <c r="H375" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12842,10 +12842,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F376" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G376" t="str">
-        <v>/send-sos</v>
+        <v>/tracking</v>
       </c>
       <c r="H376" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12871,10 +12871,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F377" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G377" t="str">
-        <v>/settings</v>
+        <v>/verify-email</v>
       </c>
       <c r="H377" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -12900,10 +12900,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F378" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G378" t="str">
-        <v>/tracking</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H378" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13132,10 +13132,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F386" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G386" t="str">
-        <v>/history</v>
+        <v>/forgot-password</v>
       </c>
       <c r="H386" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13161,10 +13161,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F387" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/EmergencyHistory.tsx</v>
       </c>
       <c r="G387" t="str">
-        <v>/login</v>
+        <v>/history</v>
       </c>
       <c r="H387" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13190,10 +13190,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F388" t="str">
-        <v>src/pages/UserProfile.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="G388" t="str">
-        <v>/profile</v>
+        <v>/login</v>
       </c>
       <c r="H388" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13219,10 +13219,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F389" t="str">
-        <v>src/pages/Registration.tsx</v>
+        <v>src/pages/UserProfile.tsx</v>
       </c>
       <c r="G389" t="str">
-        <v>/register</v>
+        <v>/profile</v>
       </c>
       <c r="H389" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13248,10 +13248,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F390" t="str">
-        <v>src/pages/SendSOS.tsx</v>
+        <v>src/pages/Registration.tsx</v>
       </c>
       <c r="G390" t="str">
-        <v>/send-sos</v>
+        <v>/register</v>
       </c>
       <c r="H390" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13277,10 +13277,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F391" t="str">
-        <v>src/pages/Settings.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G391" t="str">
-        <v>/settings</v>
+        <v>/reset-password</v>
       </c>
       <c r="H391" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13306,10 +13306,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F392" t="str">
-        <v>src/pages/LiveTracking.tsx</v>
+        <v>src/pages/SendSOS.tsx</v>
       </c>
       <c r="G392" t="str">
-        <v>/tracking</v>
+        <v>/send-sos</v>
       </c>
       <c r="H392" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13335,10 +13335,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F393" t="str">
-        <v>src/pages/VolunteerDashboard.tsx</v>
+        <v>src/pages/Settings.tsx</v>
       </c>
       <c r="G393" t="str">
-        <v>/volunteer</v>
+        <v>/settings</v>
       </c>
       <c r="H393" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13364,10 +13364,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F394" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/LiveTracking.tsx</v>
       </c>
       <c r="G394" t="str">
-        <v>*</v>
+        <v>/tracking</v>
       </c>
       <c r="H394" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13393,10 +13393,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F395" t="str">
-        <v>src/pages/LandingPage.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G395" t="str">
-        <v>/</v>
+        <v>/verify-email</v>
       </c>
       <c r="H395" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13422,10 +13422,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F396" t="str">
-        <v>src/pages/AdminDashboard.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G396" t="str">
-        <v>/admin</v>
+        <v>/verify-email-pending</v>
       </c>
       <c r="H396" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13451,10 +13451,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F397" t="str">
-        <v>src/pages/EmergencyChat.tsx</v>
+        <v>src/pages/VolunteerDashboard.tsx</v>
       </c>
       <c r="G397" t="str">
-        <v>/chat</v>
+        <v>/volunteer</v>
       </c>
       <c r="H397" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13480,10 +13480,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F398" t="str">
-        <v>src/pages/EmergencyContacts.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="G398" t="str">
-        <v>/contacts</v>
+        <v>*</v>
       </c>
       <c r="H398" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13509,10 +13509,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F399" t="str">
-        <v>src/pages/Dashboard.tsx</v>
+        <v>src/pages/LandingPage.tsx</v>
       </c>
       <c r="G399" t="str">
-        <v>/dashboard</v>
+        <v>/</v>
       </c>
       <c r="H399" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13538,10 +13538,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F400" t="str">
-        <v>src/pages/EmergencyHistory.tsx</v>
+        <v>src/pages/AdminDashboard.tsx</v>
       </c>
       <c r="G400" t="str">
-        <v>/history</v>
+        <v>/admin</v>
       </c>
       <c r="H400" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>
@@ -13567,10 +13567,10 @@
         <v>No evidence of risky behavior detected during static assessment.</v>
       </c>
       <c r="F401" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>src/pages/EmergencyChat.tsx</v>
       </c>
       <c r="G401" t="str">
-        <v>/login</v>
+        <v>/chat</v>
       </c>
       <c r="H401" t="str">
         <v>Maintain current implementation and monitor for future issues.</v>

--- a/reports/Security Findings.xlsx
+++ b/reports/Security Findings.xlsx
@@ -414,7 +414,7 @@
         <v>Generated At</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-08-01T10:50:47.052Z</v>
+        <v>2026-08-08T07:14:27.173Z</v>
       </c>
     </row>
     <row r="3">

--- a/reports/Security Findings.xlsx
+++ b/reports/Security Findings.xlsx
@@ -414,7 +414,7 @@
         <v>Generated At</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-08-08T07:14:27.173Z</v>
+        <v>2026-08-09T18:19:45.086Z</v>
       </c>
     </row>
     <row r="3">
